--- a/TOR330 Data/5. Clean Data for Data Visualisation/Anomalies Tracker/TOR330_negative_duration_checkpoints_bib_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/Anomalies Tracker/TOR330_negative_duration_checkpoints_bib_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="52">
   <si>
     <t>PK</t>
   </si>
@@ -70,10 +70,13 @@
     <t>Stage</t>
   </si>
   <si>
+    <t>Checkpoint Duration</t>
+  </si>
+  <si>
+    <t>Running Total Checkpoint Duration</t>
+  </si>
+  <si>
     <t>Missed Last Checkpoint</t>
-  </si>
-  <si>
-    <t>Checkpoint Duration</t>
   </si>
   <si>
     <t>Missed Checkpoint Allocated Time</t>
@@ -529,10 +532,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,45 +608,48 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>2023</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
+        <v>31</v>
+      </c>
+      <c r="D2">
+        <v>334</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="3">
+        <v>44</v>
+      </c>
+      <c r="L2">
         <v>-0.05702546296296297</v>
       </c>
       <c r="M2">
         <v>-4927</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2">
         <v>1.488993055555556</v>
       </c>
       <c r="O2">
@@ -653,59 +659,62 @@
         <v>45182</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3">
+        <v>47</v>
+      </c>
+      <c r="S2">
         <v>0.75</v>
       </c>
-      <c r="U2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+      <c r="T2">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>2023</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="D3">
+        <v>343</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="3">
+        <v>45</v>
+      </c>
+      <c r="L3">
         <v>-0.0003935185185185185</v>
       </c>
       <c r="M3">
         <v>-34</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3">
         <v>3.047986111111111</v>
       </c>
       <c r="O3">
@@ -715,59 +724,62 @@
         <v>45183.04166666666</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" s="3">
+        <v>48</v>
+      </c>
+      <c r="S3">
         <v>0.08333333333333333</v>
       </c>
-      <c r="U3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="T3">
+        <v>3.625</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>2023</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>1291</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="3">
+        <v>46</v>
+      </c>
+      <c r="L4">
         <v>-0.0001157407407407407</v>
       </c>
       <c r="M4">
         <v>-10</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4">
         <v>1.454675925925926</v>
       </c>
       <c r="O4">
@@ -777,59 +789,62 @@
         <v>45181.33333333334</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
+        <v>49</v>
+      </c>
+      <c r="S4">
         <v>0.08333333333333333</v>
       </c>
-      <c r="U4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="T4">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>423</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="3">
+        <v>46</v>
+      </c>
+      <c r="L5">
         <v>-0.02489583333333333</v>
       </c>
       <c r="M5">
         <v>-2151</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5">
         <v>4.427974537037037</v>
       </c>
       <c r="O5">
@@ -839,59 +854,62 @@
         <v>45184.79166666666</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
+        <v>50</v>
+      </c>
+      <c r="S5">
         <v>0.08333333333333333</v>
       </c>
-      <c r="U5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="T5">
+        <v>5.375</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>51</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
         <v>29</v>
       </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
       <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>1334</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="3">
+        <v>46</v>
+      </c>
+      <c r="L6">
         <v>-0.0002083333333333333</v>
       </c>
       <c r="M6">
         <v>-18</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6">
         <v>1.483113425925926</v>
       </c>
       <c r="O6">
@@ -901,18 +919,1321 @@
         <v>45181.33333333334</v>
       </c>
       <c r="R6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T6">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>334</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M7">
+        <v>-4927</v>
+      </c>
+      <c r="N7">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O7">
+        <v>128649</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>45182</v>
+      </c>
+      <c r="R7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S7">
+        <v>0.75</v>
+      </c>
+      <c r="T7">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>51</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>2023</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>343</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M8">
+        <v>-34</v>
+      </c>
+      <c r="N8">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O8">
+        <v>263346</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="R8" t="s">
         <v>48</v>
       </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
+      <c r="S8">
         <v>0.08333333333333333</v>
       </c>
-      <c r="U6" t="s">
+      <c r="T8">
+        <v>3.625</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>51</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>2023</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>1291</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M9">
+        <v>-10</v>
+      </c>
+      <c r="N9">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O9">
+        <v>125684</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R9" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T9">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10">
+        <v>2023</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>423</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M10">
+        <v>-2151</v>
+      </c>
+      <c r="N10">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O10">
+        <v>382577</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="R10" t="s">
         <v>50</v>
       </c>
-      <c r="V6" t="b">
+      <c r="S10">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T10">
+        <v>5.375</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
+        <v>51</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>1334</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M11">
+        <v>-18</v>
+      </c>
+      <c r="N11">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O11">
+        <v>128141</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R11" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T11">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
+        <v>51</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <v>2023</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>334</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M12">
+        <v>-4927</v>
+      </c>
+      <c r="N12">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O12">
+        <v>128649</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>45182</v>
+      </c>
+      <c r="R12" t="s">
+        <v>47</v>
+      </c>
+      <c r="S12">
+        <v>0.75</v>
+      </c>
+      <c r="T12">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
+        <v>51</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>343</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M13">
+        <v>-34</v>
+      </c>
+      <c r="N13">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O13">
+        <v>263346</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="R13" t="s">
+        <v>48</v>
+      </c>
+      <c r="S13">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T13">
+        <v>3.625</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>51</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>1291</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M14">
+        <v>-10</v>
+      </c>
+      <c r="N14">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O14">
+        <v>125684</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R14" t="s">
+        <v>49</v>
+      </c>
+      <c r="S14">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T14">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>51</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>423</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K15" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M15">
+        <v>-2151</v>
+      </c>
+      <c r="N15">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O15">
+        <v>382577</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="R15" t="s">
+        <v>50</v>
+      </c>
+      <c r="S15">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T15">
+        <v>5.375</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="s">
+        <v>51</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>1334</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M16">
+        <v>-18</v>
+      </c>
+      <c r="N16">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O16">
+        <v>128141</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R16" t="s">
+        <v>49</v>
+      </c>
+      <c r="S16">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T16">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="s">
+        <v>51</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>334</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J17" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M17">
+        <v>-4927</v>
+      </c>
+      <c r="N17">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O17">
+        <v>128649</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>45182</v>
+      </c>
+      <c r="R17" t="s">
+        <v>47</v>
+      </c>
+      <c r="S17">
+        <v>0.75</v>
+      </c>
+      <c r="T17">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="s">
+        <v>51</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>343</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K18" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M18">
+        <v>-34</v>
+      </c>
+      <c r="N18">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O18">
+        <v>263346</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="R18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T18">
+        <v>3.625</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="s">
+        <v>51</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>2023</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19">
+        <v>1291</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M19">
+        <v>-10</v>
+      </c>
+      <c r="N19">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O19">
+        <v>125684</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R19" t="s">
+        <v>49</v>
+      </c>
+      <c r="S19">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T19">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="s">
+        <v>51</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>423</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M20">
+        <v>-2151</v>
+      </c>
+      <c r="N20">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O20">
+        <v>382577</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="R20" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T20">
+        <v>5.375</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="s">
+        <v>51</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21">
+        <v>1334</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M21">
+        <v>-18</v>
+      </c>
+      <c r="N21">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O21">
+        <v>128141</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R21" t="s">
+        <v>49</v>
+      </c>
+      <c r="S21">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T21">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="s">
+        <v>51</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="3">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M22">
+        <v>-4927</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O22">
+        <v>128649</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>45182</v>
+      </c>
+      <c r="R22" t="s">
+        <v>47</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="T22" s="3">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
+        <v>51</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M23">
+        <v>-34</v>
+      </c>
+      <c r="N23" s="3">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O23">
+        <v>263346</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="R23" t="s">
+        <v>48</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T23" s="3">
+        <v>3.625</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="s">
+        <v>51</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M24">
+        <v>-10</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O24">
+        <v>125684</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R24" t="s">
+        <v>49</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
+        <v>51</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L25" s="3">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M25">
+        <v>-2151</v>
+      </c>
+      <c r="N25" s="3">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O25">
+        <v>382577</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="R25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T25" s="3">
+        <v>5.375</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="s">
+        <v>51</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K26" t="s">
+        <v>46</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M26">
+        <v>-18</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O26">
+        <v>128141</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="R26" t="s">
+        <v>49</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
+        <v>51</v>
+      </c>
+      <c r="W26" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TOR330 Data/5. Clean Data for Data Visualisation/Anomalies Tracker/TOR330_negative_duration_checkpoints_bib_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/Anomalies Tracker/TOR330_negative_duration_checkpoints_bib_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="67">
   <si>
     <t>PK</t>
   </si>
@@ -91,6 +91,27 @@
     <t>Missed Diff_seconds</t>
   </si>
   <si>
+    <t>TOR330_2021_162</t>
+  </si>
+  <si>
+    <t>TOR330_2022_275</t>
+  </si>
+  <si>
+    <t>TOR330_2022_127</t>
+  </si>
+  <si>
+    <t>TOR330_2022_549</t>
+  </si>
+  <si>
+    <t>TOR330_2022_1005</t>
+  </si>
+  <si>
+    <t>TOR330_2022_1205</t>
+  </si>
+  <si>
+    <t>TOR330_2022_1268</t>
+  </si>
+  <si>
     <t>TOR330_2023_334</t>
   </si>
   <si>
@@ -106,67 +127,91 @@
     <t>TOR330_2023_1334</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>TOR330_2024_404</t>
+  </si>
+  <si>
+    <t>TOR330_2024_1367</t>
+  </si>
+  <si>
+    <t>2024</t>
   </si>
   <si>
     <t>TOR330</t>
   </si>
   <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>1291</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>1334</t>
+    <t>404</t>
+  </si>
+  <si>
+    <t>1367</t>
   </si>
   <si>
     <t>Finished at Courmayeur</t>
   </si>
   <si>
+    <t>Finished at Bosses</t>
+  </si>
+  <si>
+    <t>Finished at Rifugio Frassati</t>
+  </si>
+  <si>
+    <t>DNF</t>
+  </si>
+  <si>
+    <t>Cogne</t>
+  </si>
+  <si>
+    <t>No Wave in 2021</t>
+  </si>
+  <si>
     <t>Wave1</t>
   </si>
   <si>
     <t>Wave2</t>
   </si>
   <si>
+    <t>Ollomont OUT</t>
+  </si>
+  <si>
+    <t>Gressoney OUT</t>
+  </si>
+  <si>
+    <t>Valtournenche OUT</t>
+  </si>
+  <si>
     <t>Donnas IN</t>
   </si>
   <si>
-    <t>Gressoney OUT</t>
-  </si>
-  <si>
     <t>Cogne OUT</t>
   </si>
   <si>
-    <t>Ollomont OUT</t>
+    <t>Sub-140</t>
+  </si>
+  <si>
+    <t>Sub-90</t>
+  </si>
+  <si>
+    <t>Sub-100</t>
   </si>
   <si>
     <t>Sub-130</t>
   </si>
   <si>
-    <t>Sub-140</t>
-  </si>
-  <si>
     <t>Sub-150</t>
   </si>
   <si>
+    <t>Time Spent in Ollomont</t>
+  </si>
+  <si>
+    <t>Time Spent in Gressoney</t>
+  </si>
+  <si>
+    <t>Time Spent in Valtournenche</t>
+  </si>
+  <si>
     <t>Stage 3</t>
   </si>
   <si>
-    <t>Time Spent in Gressoney</t>
-  </si>
-  <si>
     <t>Time Spent in Cogne</t>
-  </si>
-  <si>
-    <t>Time Spent in Ollomont</t>
   </si>
   <si>
     <t>Within Allocated Time</t>
@@ -532,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -617,61 +662,61 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>334</v>
+        <v>162</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J2" s="2">
-        <v>45180.90565972222</v>
+        <v>44456.22016203704</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L2">
-        <v>-0.05702546296296297</v>
+        <v>-0.001018518518518518</v>
       </c>
       <c r="M2">
-        <v>-4927</v>
+        <v>-88</v>
       </c>
       <c r="N2">
-        <v>1.488993055555556</v>
+        <v>4.803495370370371</v>
       </c>
       <c r="O2">
-        <v>128649</v>
+        <v>415022</v>
       </c>
       <c r="Q2" s="2">
-        <v>45182</v>
+        <v>44456.79166666666</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="S2">
-        <v>0.75</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T2">
-        <v>2.583333333333333</v>
+        <v>5.375</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
@@ -682,49 +727,49 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J3" s="2">
-        <v>45182.46465277778</v>
+        <v>44817.39240740741</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L3">
-        <v>-0.0003935185185185185</v>
+        <v>-0.003252314814814815</v>
       </c>
       <c r="M3">
-        <v>-34</v>
+        <v>-281</v>
       </c>
       <c r="N3">
-        <v>3.047986111111111</v>
+        <v>1.975740740740741</v>
       </c>
       <c r="O3">
-        <v>263346</v>
+        <v>170704</v>
       </c>
       <c r="Q3" s="2">
-        <v>45183.04166666666</v>
+        <v>44819.04166666666</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="S3">
         <v>0.08333333333333333</v>
@@ -736,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -747,61 +792,61 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>1291</v>
+        <v>127</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J4" s="2">
-        <v>45180.95467592592</v>
+        <v>44818.26855324074</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="L4">
-        <v>-0.0001157407407407407</v>
+        <v>-0.0005439814814814814</v>
       </c>
       <c r="M4">
-        <v>-10</v>
+        <v>-47</v>
       </c>
       <c r="N4">
-        <v>1.454675925925926</v>
+        <v>2.851886574074074</v>
       </c>
       <c r="O4">
-        <v>125684</v>
+        <v>246403</v>
       </c>
       <c r="Q4" s="2">
-        <v>45181.33333333334</v>
+        <v>44819.875</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="S4">
         <v>0.08333333333333333</v>
       </c>
       <c r="T4">
-        <v>1.833333333333333</v>
+        <v>4.458333333333333</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
@@ -812,49 +857,49 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>423</v>
+        <v>549</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J5" s="2">
-        <v>45183.8446412037</v>
+        <v>44820.2553125</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L5">
-        <v>-0.02489583333333333</v>
+        <v>-0.0003587962962962963</v>
       </c>
       <c r="M5">
-        <v>-2151</v>
+        <v>-31</v>
       </c>
       <c r="N5">
-        <v>4.427974537037037</v>
+        <v>4.838645833333334</v>
       </c>
       <c r="O5">
-        <v>382577</v>
+        <v>418059</v>
       </c>
       <c r="Q5" s="2">
-        <v>45184.79166666666</v>
+        <v>44820.79166666666</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="S5">
         <v>0.08333333333333333</v>
@@ -866,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
@@ -877,61 +922,58 @@
         <v>29</v>
       </c>
       <c r="B6">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>1334</v>
+        <v>1005</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J6" s="2">
-        <v>45180.98311342593</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
+        <v>44819.50680555555</v>
       </c>
       <c r="L6">
-        <v>-0.0002083333333333333</v>
+        <v>-0.0002777777777777778</v>
       </c>
       <c r="M6">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="N6">
-        <v>1.483113425925926</v>
+        <v>4.006805555555555</v>
       </c>
       <c r="O6">
-        <v>128141</v>
+        <v>346188</v>
       </c>
       <c r="Q6" s="2">
-        <v>45181.33333333334</v>
+        <v>44819.95833333334</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="S6">
         <v>0.08333333333333333</v>
       </c>
       <c r="T6">
-        <v>1.833333333333333</v>
+        <v>4.458333333333333</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
@@ -939,64 +981,61 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>334</v>
+        <v>1205</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="J7" s="2">
-        <v>45180.90565972222</v>
-      </c>
-      <c r="K7" t="s">
-        <v>44</v>
+        <v>44818.92413194444</v>
       </c>
       <c r="L7">
-        <v>-0.05702546296296297</v>
+        <v>-0.0002199074074074074</v>
       </c>
       <c r="M7">
-        <v>-4927</v>
+        <v>-19</v>
       </c>
       <c r="N7">
-        <v>1.488993055555556</v>
+        <v>3.424131944444444</v>
       </c>
       <c r="O7">
-        <v>128649</v>
+        <v>295845</v>
       </c>
       <c r="Q7" s="2">
-        <v>45182</v>
+        <v>44819.125</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="S7">
-        <v>0.75</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T7">
-        <v>2.583333333333333</v>
+        <v>3.625</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
@@ -1004,52 +1043,49 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B8">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>343</v>
+        <v>1268</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J8" s="2">
-        <v>45182.46465277778</v>
-      </c>
-      <c r="K8" t="s">
-        <v>45</v>
+        <v>44818.92489583333</v>
       </c>
       <c r="L8">
-        <v>-0.0003935185185185185</v>
+        <v>-0.0008333333333333334</v>
       </c>
       <c r="M8">
-        <v>-34</v>
+        <v>-72</v>
       </c>
       <c r="N8">
-        <v>3.047986111111111</v>
+        <v>3.424895833333333</v>
       </c>
       <c r="O8">
-        <v>263346</v>
+        <v>295911</v>
       </c>
       <c r="Q8" s="2">
-        <v>45183.04166666666</v>
+        <v>44819.125</v>
       </c>
       <c r="R8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="S8">
         <v>0.08333333333333333</v>
@@ -1061,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
@@ -1069,64 +1105,64 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>2023</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>1291</v>
+        <v>334</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J9" s="2">
-        <v>45180.95467592592</v>
+        <v>45180.90565972222</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="L9">
-        <v>-0.0001157407407407407</v>
+        <v>-0.05702546296296297</v>
       </c>
       <c r="M9">
-        <v>-10</v>
+        <v>-4927</v>
       </c>
       <c r="N9">
-        <v>1.454675925925926</v>
+        <v>1.488993055555556</v>
       </c>
       <c r="O9">
-        <v>125684</v>
+        <v>128649</v>
       </c>
       <c r="Q9" s="2">
-        <v>45181.33333333334</v>
+        <v>45182</v>
       </c>
       <c r="R9" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="S9">
-        <v>0.08333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="T9">
-        <v>1.833333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
@@ -1134,64 +1170,64 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>2023</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D10">
-        <v>423</v>
+        <v>343</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J10" s="2">
-        <v>45183.8446412037</v>
+        <v>45182.46465277778</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L10">
-        <v>-0.02489583333333333</v>
+        <v>-0.0003935185185185185</v>
       </c>
       <c r="M10">
-        <v>-2151</v>
+        <v>-34</v>
       </c>
       <c r="N10">
-        <v>4.427974537037037</v>
+        <v>3.047986111111111</v>
       </c>
       <c r="O10">
-        <v>382577</v>
+        <v>263346</v>
       </c>
       <c r="Q10" s="2">
-        <v>45184.79166666666</v>
+        <v>45183.04166666666</v>
       </c>
       <c r="R10" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="S10">
         <v>0.08333333333333333</v>
       </c>
       <c r="T10">
-        <v>5.375</v>
+        <v>3.625</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
@@ -1199,52 +1235,52 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>1334</v>
+        <v>1291</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="J11" s="2">
-        <v>45180.98311342593</v>
+        <v>45180.95467592592</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="L11">
-        <v>-0.0002083333333333333</v>
+        <v>-0.0001157407407407407</v>
       </c>
       <c r="M11">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="N11">
-        <v>1.483113425925926</v>
+        <v>1.454675925925926</v>
       </c>
       <c r="O11">
-        <v>128141</v>
+        <v>125684</v>
       </c>
       <c r="Q11" s="2">
         <v>45181.33333333334</v>
       </c>
       <c r="R11" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="S11">
         <v>0.08333333333333333</v>
@@ -1256,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
@@ -1264,64 +1300,64 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D12">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J12" s="2">
-        <v>45180.90565972222</v>
+        <v>45183.8446412037</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L12">
-        <v>-0.05702546296296297</v>
+        <v>-0.02489583333333333</v>
       </c>
       <c r="M12">
-        <v>-4927</v>
+        <v>-2151</v>
       </c>
       <c r="N12">
-        <v>1.488993055555556</v>
+        <v>4.427974537037037</v>
       </c>
       <c r="O12">
-        <v>128649</v>
+        <v>382577</v>
       </c>
       <c r="Q12" s="2">
-        <v>45182</v>
+        <v>45184.79166666666</v>
       </c>
       <c r="R12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="S12">
-        <v>0.75</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T12">
-        <v>2.583333333333333</v>
+        <v>5.375</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
@@ -1329,64 +1365,64 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B13">
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>343</v>
+        <v>1334</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="J13" s="2">
-        <v>45182.46465277778</v>
+        <v>45180.98311342593</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L13">
-        <v>-0.0003935185185185185</v>
+        <v>-0.0002083333333333333</v>
       </c>
       <c r="M13">
-        <v>-34</v>
+        <v>-18</v>
       </c>
       <c r="N13">
-        <v>3.047986111111111</v>
+        <v>1.483113425925926</v>
       </c>
       <c r="O13">
-        <v>263346</v>
+        <v>128141</v>
       </c>
       <c r="Q13" s="2">
-        <v>45183.04166666666</v>
+        <v>45181.33333333334</v>
       </c>
       <c r="R13" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="S13">
         <v>0.08333333333333333</v>
       </c>
       <c r="T13">
-        <v>3.625</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
@@ -1394,64 +1430,64 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14">
-        <v>2023</v>
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>1291</v>
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J14" s="2">
-        <v>45180.95467592592</v>
+        <v>45546.77756944444</v>
       </c>
       <c r="K14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14">
-        <v>-0.0001157407407407407</v>
+        <v>59</v>
+      </c>
+      <c r="L14" s="3">
+        <v>-0.007534722222222222</v>
       </c>
       <c r="M14">
-        <v>-10</v>
-      </c>
-      <c r="N14">
-        <v>1.454675925925926</v>
+        <v>-651</v>
+      </c>
+      <c r="N14" s="3">
+        <v>3.360902777777778</v>
       </c>
       <c r="O14">
-        <v>125684</v>
+        <v>290382</v>
       </c>
       <c r="Q14" s="2">
-        <v>45181.33333333334</v>
+        <v>45547.875</v>
       </c>
       <c r="R14" t="s">
-        <v>49</v>
-      </c>
-      <c r="S14">
+        <v>63</v>
+      </c>
+      <c r="S14" s="3">
         <v>0.08333333333333333</v>
       </c>
-      <c r="T14">
-        <v>1.833333333333333</v>
+      <c r="T14" s="3">
+        <v>4.458333333333333</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
       </c>
       <c r="V14" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
@@ -1459,781 +1495,72 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15">
-        <v>2023</v>
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15">
-        <v>423</v>
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
       </c>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J15" s="2">
-        <v>45183.8446412037</v>
+        <v>45545.14299768519</v>
       </c>
       <c r="K15" t="s">
         <v>46</v>
       </c>
-      <c r="L15">
-        <v>-0.02489583333333333</v>
+      <c r="L15" s="3">
+        <v>-0.0003587962962962963</v>
       </c>
       <c r="M15">
-        <v>-2151</v>
-      </c>
-      <c r="N15">
-        <v>4.427974537037037</v>
+        <v>-31</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1.642997685185185</v>
       </c>
       <c r="O15">
-        <v>382577</v>
+        <v>141955</v>
+      </c>
+      <c r="P15" t="s">
+        <v>55</v>
       </c>
       <c r="Q15" s="2">
-        <v>45184.79166666666</v>
+        <v>45545.33333333334</v>
       </c>
       <c r="R15" t="s">
-        <v>50</v>
-      </c>
-      <c r="S15">
+        <v>65</v>
+      </c>
+      <c r="S15" s="3">
         <v>0.08333333333333333</v>
       </c>
-      <c r="T15">
-        <v>5.375</v>
+      <c r="T15" s="3">
+        <v>1.833333333333333</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
       <c r="V15" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16">
-        <v>2023</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16">
-        <v>1334</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" s="2">
-        <v>45180.98311342593</v>
-      </c>
-      <c r="K16" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16">
-        <v>-0.0002083333333333333</v>
-      </c>
-      <c r="M16">
-        <v>-18</v>
-      </c>
-      <c r="N16">
-        <v>1.483113425925926</v>
-      </c>
-      <c r="O16">
-        <v>128141</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>45181.33333333334</v>
-      </c>
-      <c r="R16" t="s">
-        <v>49</v>
-      </c>
-      <c r="S16">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T16">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="s">
-        <v>51</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17">
-        <v>334</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="2">
-        <v>45180.90565972222</v>
-      </c>
-      <c r="K17" t="s">
-        <v>44</v>
-      </c>
-      <c r="L17">
-        <v>-0.05702546296296297</v>
-      </c>
-      <c r="M17">
-        <v>-4927</v>
-      </c>
-      <c r="N17">
-        <v>1.488993055555556</v>
-      </c>
-      <c r="O17">
-        <v>128649</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>45182</v>
-      </c>
-      <c r="R17" t="s">
-        <v>47</v>
-      </c>
-      <c r="S17">
-        <v>0.75</v>
-      </c>
-      <c r="T17">
-        <v>2.583333333333333</v>
-      </c>
-      <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="V17" t="s">
-        <v>51</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18">
-        <v>2023</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18">
-        <v>343</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="2">
-        <v>45182.46465277778</v>
-      </c>
-      <c r="K18" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18">
-        <v>-0.0003935185185185185</v>
-      </c>
-      <c r="M18">
-        <v>-34</v>
-      </c>
-      <c r="N18">
-        <v>3.047986111111111</v>
-      </c>
-      <c r="O18">
-        <v>263346</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>45183.04166666666</v>
-      </c>
-      <c r="R18" t="s">
-        <v>48</v>
-      </c>
-      <c r="S18">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T18">
-        <v>3.625</v>
-      </c>
-      <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="s">
-        <v>51</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19">
-        <v>2023</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19">
-        <v>1291</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" t="s">
-        <v>39</v>
-      </c>
-      <c r="I19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="2">
-        <v>45180.95467592592</v>
-      </c>
-      <c r="K19" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19">
-        <v>-0.0001157407407407407</v>
-      </c>
-      <c r="M19">
-        <v>-10</v>
-      </c>
-      <c r="N19">
-        <v>1.454675925925926</v>
-      </c>
-      <c r="O19">
-        <v>125684</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>45181.33333333334</v>
-      </c>
-      <c r="R19" t="s">
-        <v>49</v>
-      </c>
-      <c r="S19">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T19">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="s">
-        <v>51</v>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20">
-        <v>423</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="2">
-        <v>45183.8446412037</v>
-      </c>
-      <c r="K20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20">
-        <v>-0.02489583333333333</v>
-      </c>
-      <c r="M20">
-        <v>-2151</v>
-      </c>
-      <c r="N20">
-        <v>4.427974537037037</v>
-      </c>
-      <c r="O20">
-        <v>382577</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>45184.79166666666</v>
-      </c>
-      <c r="R20" t="s">
-        <v>50</v>
-      </c>
-      <c r="S20">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T20">
-        <v>5.375</v>
-      </c>
-      <c r="U20" t="b">
-        <v>0</v>
-      </c>
-      <c r="V20" t="s">
-        <v>51</v>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
-      <c r="A21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21">
-        <v>1334</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="2">
-        <v>45180.98311342593</v>
-      </c>
-      <c r="K21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21">
-        <v>-0.0002083333333333333</v>
-      </c>
-      <c r="M21">
-        <v>-18</v>
-      </c>
-      <c r="N21">
-        <v>1.483113425925926</v>
-      </c>
-      <c r="O21">
-        <v>128141</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>45181.33333333334</v>
-      </c>
-      <c r="R21" t="s">
-        <v>49</v>
-      </c>
-      <c r="S21">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T21">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="U21" t="b">
-        <v>0</v>
-      </c>
-      <c r="V21" t="s">
-        <v>51</v>
-      </c>
-      <c r="W21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="2">
-        <v>45180.90565972222</v>
-      </c>
-      <c r="K22" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" s="3">
-        <v>-0.05702546296296297</v>
-      </c>
-      <c r="M22">
-        <v>-4927</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1.488993055555556</v>
-      </c>
-      <c r="O22">
-        <v>128649</v>
-      </c>
-      <c r="Q22" s="2">
-        <v>45182</v>
-      </c>
-      <c r="R22" t="s">
-        <v>47</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="T22" s="3">
-        <v>2.583333333333333</v>
-      </c>
-      <c r="U22" t="b">
-        <v>0</v>
-      </c>
-      <c r="V22" t="s">
-        <v>51</v>
-      </c>
-      <c r="W22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" t="s">
-        <v>38</v>
-      </c>
-      <c r="I23" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="2">
-        <v>45182.46465277778</v>
-      </c>
-      <c r="K23" t="s">
-        <v>45</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-0.0003935185185185185</v>
-      </c>
-      <c r="M23">
-        <v>-34</v>
-      </c>
-      <c r="N23" s="3">
-        <v>3.047986111111111</v>
-      </c>
-      <c r="O23">
-        <v>263346</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>45183.04166666666</v>
-      </c>
-      <c r="R23" t="s">
-        <v>48</v>
-      </c>
-      <c r="S23" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T23" s="3">
-        <v>3.625</v>
-      </c>
-      <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="s">
-        <v>51</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="2">
-        <v>45180.95467592592</v>
-      </c>
-      <c r="K24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-0.0001157407407407407</v>
-      </c>
-      <c r="M24">
-        <v>-10</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1.454675925925926</v>
-      </c>
-      <c r="O24">
-        <v>125684</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>45181.33333333334</v>
-      </c>
-      <c r="R24" t="s">
-        <v>49</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="U24" t="b">
-        <v>0</v>
-      </c>
-      <c r="V24" t="s">
-        <v>51</v>
-      </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>37</v>
-      </c>
-      <c r="H25" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="2">
-        <v>45183.8446412037</v>
-      </c>
-      <c r="K25" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="3">
-        <v>-0.02489583333333333</v>
-      </c>
-      <c r="M25">
-        <v>-2151</v>
-      </c>
-      <c r="N25" s="3">
-        <v>4.427974537037037</v>
-      </c>
-      <c r="O25">
-        <v>382577</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>45184.79166666666</v>
-      </c>
-      <c r="R25" t="s">
-        <v>50</v>
-      </c>
-      <c r="S25" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T25" s="3">
-        <v>5.375</v>
-      </c>
-      <c r="U25" t="b">
-        <v>0</v>
-      </c>
-      <c r="V25" t="s">
-        <v>51</v>
-      </c>
-      <c r="W25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="2">
-        <v>45180.98311342593</v>
-      </c>
-      <c r="K26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-0.0002083333333333333</v>
-      </c>
-      <c r="M26">
-        <v>-18</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1.483113425925926</v>
-      </c>
-      <c r="O26">
-        <v>128141</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>45181.33333333334</v>
-      </c>
-      <c r="R26" t="s">
-        <v>49</v>
-      </c>
-      <c r="S26" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="U26" t="b">
-        <v>0</v>
-      </c>
-      <c r="V26" t="s">
-        <v>51</v>
-      </c>
-      <c r="W26" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TOR330 Data/5. Clean Data for Data Visualisation/Anomalies Tracker/TOR330_negative_duration_checkpoints_bib_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/Anomalies Tracker/TOR330_negative_duration_checkpoints_bib_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="122">
   <si>
     <t>PK</t>
   </si>
@@ -133,16 +133,136 @@
     <t>TOR330_2024_1367</t>
   </si>
   <si>
-    <t>2024</t>
+    <t>TOR330_2025_12</t>
+  </si>
+  <si>
+    <t>TOR330_2025_7</t>
+  </si>
+  <si>
+    <t>TOR330_2025_54</t>
+  </si>
+  <si>
+    <t>TOR330_2025_638</t>
+  </si>
+  <si>
+    <t>TOR330_2025_525</t>
+  </si>
+  <si>
+    <t>TOR330_2025_308</t>
+  </si>
+  <si>
+    <t>TOR330_2025_355</t>
+  </si>
+  <si>
+    <t>TOR330_2025_384</t>
+  </si>
+  <si>
+    <t>TOR330_2025_546</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1096</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1070</t>
+  </si>
+  <si>
+    <t>TOR330_2025_651</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1190</t>
+  </si>
+  <si>
+    <t>TOR330_2025_95</t>
+  </si>
+  <si>
+    <t>TOR330_2025_403</t>
+  </si>
+  <si>
+    <t>TOR330_2025_656</t>
+  </si>
+  <si>
+    <t>TOR330_2025_661</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1131</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1187</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1415</t>
+  </si>
+  <si>
+    <t>TOR330_2025_1497</t>
+  </si>
+  <si>
+    <t>2025</t>
   </si>
   <si>
     <t>TOR330</t>
   </si>
   <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>1367</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>638</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>651</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>656</t>
+  </si>
+  <si>
+    <t>661</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>1497</t>
   </si>
   <si>
     <t>Finished at Courmayeur</t>
@@ -160,6 +280,18 @@
     <t>Cogne</t>
   </si>
   <si>
+    <t>Goilles</t>
+  </si>
+  <si>
+    <t>Valgrisenche</t>
+  </si>
+  <si>
+    <t>Gressoney</t>
+  </si>
+  <si>
+    <t>Pas Entre Deux Sauts</t>
+  </si>
+  <si>
     <t>No Wave in 2021</t>
   </si>
   <si>
@@ -184,6 +316,15 @@
     <t>Cogne OUT</t>
   </si>
   <si>
+    <t>Donnas OUT</t>
+  </si>
+  <si>
+    <t>Niel La Gruba</t>
+  </si>
+  <si>
+    <t>Valgrisenche OUT</t>
+  </si>
+  <si>
     <t>Sub-140</t>
   </si>
   <si>
@@ -199,6 +340,21 @@
     <t>Sub-150</t>
   </si>
   <si>
+    <t>Sub-70</t>
+  </si>
+  <si>
+    <t>Sub-80</t>
+  </si>
+  <si>
+    <t>Sub-120</t>
+  </si>
+  <si>
+    <t>Over-150</t>
+  </si>
+  <si>
+    <t>Gressoney IN</t>
+  </si>
+  <si>
     <t>Time Spent in Ollomont</t>
   </si>
   <si>
@@ -212,6 +368,15 @@
   </si>
   <si>
     <t>Time Spent in Cogne</t>
+  </si>
+  <si>
+    <t>Time Spent in Donnas</t>
+  </si>
+  <si>
+    <t>Stage 4</t>
+  </si>
+  <si>
+    <t>Time Spent in Valgrisenche</t>
   </si>
   <si>
     <t>Within Allocated Time</t>
@@ -577,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -665,7 +830,7 @@
         <v>2021</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D2">
         <v>162</v>
@@ -674,19 +839,19 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="J2" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K2" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="L2">
         <v>-0.001018518518518518</v>
@@ -704,7 +869,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="R2" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="S2">
         <v>0.08333333333333333</v>
@@ -716,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
@@ -730,7 +895,7 @@
         <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D3">
         <v>275</v>
@@ -739,19 +904,19 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I3" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="J3" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K3" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="L3">
         <v>-0.003252314814814815</v>
@@ -769,7 +934,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="R3" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="S3">
         <v>0.08333333333333333</v>
@@ -781,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -795,7 +960,7 @@
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>127</v>
@@ -804,19 +969,19 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="J4" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="L4">
         <v>-0.0005439814814814814</v>
@@ -834,7 +999,7 @@
         <v>44819.875</v>
       </c>
       <c r="R4" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="S4">
         <v>0.08333333333333333</v>
@@ -846,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
@@ -860,7 +1025,7 @@
         <v>2022</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D5">
         <v>549</v>
@@ -869,19 +1034,19 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="J5" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="L5">
         <v>-0.0003587962962962963</v>
@@ -899,7 +1064,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="R5" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="S5">
         <v>0.08333333333333333</v>
@@ -911,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
@@ -925,7 +1090,7 @@
         <v>2022</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D6">
         <v>1005</v>
@@ -934,13 +1099,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2">
         <v>44819.50680555555</v>
@@ -961,7 +1126,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="R6" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="S6">
         <v>0.08333333333333333</v>
@@ -973,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
@@ -987,7 +1152,7 @@
         <v>2022</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>1205</v>
@@ -996,13 +1161,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="J7" s="2">
         <v>44818.92413194444</v>
@@ -1023,7 +1188,7 @@
         <v>44819.125</v>
       </c>
       <c r="R7" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="S7">
         <v>0.08333333333333333</v>
@@ -1035,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
@@ -1049,7 +1214,7 @@
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D8">
         <v>1268</v>
@@ -1058,13 +1223,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="J8" s="2">
         <v>44818.92489583333</v>
@@ -1085,7 +1250,7 @@
         <v>44819.125</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="S8">
         <v>0.08333333333333333</v>
@@ -1097,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
@@ -1111,7 +1276,7 @@
         <v>2023</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D9">
         <v>334</v>
@@ -1120,19 +1285,19 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="J9" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K9" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="L9">
         <v>-0.05702546296296297</v>
@@ -1150,7 +1315,7 @@
         <v>45182</v>
       </c>
       <c r="R9" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="S9">
         <v>0.75</v>
@@ -1162,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
@@ -1176,7 +1341,7 @@
         <v>2023</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D10">
         <v>343</v>
@@ -1185,19 +1350,19 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="J10" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="L10">
         <v>-0.0003935185185185185</v>
@@ -1215,7 +1380,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="R10" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="S10">
         <v>0.08333333333333333</v>
@@ -1227,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
@@ -1241,7 +1406,7 @@
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>1291</v>
@@ -1250,19 +1415,19 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="J11" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="L11">
         <v>-0.0001157407407407407</v>
@@ -1280,7 +1445,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="R11" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="S11">
         <v>0.08333333333333333</v>
@@ -1292,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
@@ -1306,7 +1471,7 @@
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>423</v>
@@ -1315,19 +1480,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="J12" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="L12">
         <v>-0.02489583333333333</v>
@@ -1345,7 +1510,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="R12" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="S12">
         <v>0.08333333333333333</v>
@@ -1357,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
@@ -1371,7 +1536,7 @@
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <v>1334</v>
@@ -1380,19 +1545,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="J13" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="L13">
         <v>-0.0002083333333333333</v>
@@ -1410,7 +1575,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="R13" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="S13">
         <v>0.08333333333333333</v>
@@ -1422,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
@@ -1432,40 +1597,40 @@
       <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
-        <v>39</v>
+      <c r="B14">
+        <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
+        <v>61</v>
+      </c>
+      <c r="D14">
+        <v>404</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="J14" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="3">
+        <v>106</v>
+      </c>
+      <c r="L14">
         <v>-0.007534722222222222</v>
       </c>
       <c r="M14">
         <v>-651</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14">
         <v>3.360902777777778</v>
       </c>
       <c r="O14">
@@ -1475,19 +1640,19 @@
         <v>45547.875</v>
       </c>
       <c r="R14" t="s">
-        <v>63</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T14" s="3">
+        <v>115</v>
+      </c>
+      <c r="S14">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T14">
         <v>4.458333333333333</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
       </c>
       <c r="V14" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
@@ -1497,70 +1662,5667 @@
       <c r="A15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
-        <v>39</v>
+      <c r="B15">
+        <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
+        <v>61</v>
+      </c>
+      <c r="D15">
+        <v>1367</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="J15" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K15" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="3">
+        <v>86</v>
+      </c>
+      <c r="L15">
         <v>-0.0003587962962962963</v>
       </c>
       <c r="M15">
         <v>-31</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15">
         <v>1.642997685185185</v>
       </c>
       <c r="O15">
         <v>141955</v>
       </c>
       <c r="P15" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="Q15" s="2">
         <v>45545.33333333334</v>
       </c>
       <c r="R15" t="s">
+        <v>117</v>
+      </c>
+      <c r="S15">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T15">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="s">
+        <v>121</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="2">
+        <v>45915.42967841435</v>
+      </c>
+      <c r="K16" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16">
+        <v>-0.001164791666666667</v>
+      </c>
+      <c r="M16">
+        <v>-100.638</v>
+      </c>
+      <c r="N16">
+        <v>1.013011747685185</v>
+      </c>
+      <c r="O16">
+        <v>87524.215</v>
+      </c>
+      <c r="R16" t="s">
+        <v>118</v>
+      </c>
+      <c r="S16">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T16">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="s">
+        <v>121</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" s="2">
+        <v>45915.14942453703</v>
+      </c>
+      <c r="K17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17">
+        <v>-0.0001758796296296296</v>
+      </c>
+      <c r="M17">
+        <v>-15.196</v>
+      </c>
+      <c r="N17">
+        <v>0.7327578703703703</v>
+      </c>
+      <c r="O17">
+        <v>63310.28</v>
+      </c>
+      <c r="R17" t="s">
+        <v>117</v>
+      </c>
+      <c r="S17">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T17">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="s">
+        <v>121</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18">
+        <v>54</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="2">
+        <v>45916.01724591435</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18">
+        <v>-0.0004433912037037037</v>
+      </c>
+      <c r="M18">
+        <v>-38.309</v>
+      </c>
+      <c r="N18">
+        <v>1.600579247685185</v>
+      </c>
+      <c r="O18">
+        <v>138290.047</v>
+      </c>
+      <c r="R18" t="s">
+        <v>118</v>
+      </c>
+      <c r="S18">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T18">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="s">
+        <v>121</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19">
+        <v>638</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="2">
+        <v>45917.74812557871</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>-0.002106851851851852</v>
+      </c>
+      <c r="M19">
+        <v>-182.032</v>
+      </c>
+      <c r="N19">
+        <v>3.331458912037037</v>
+      </c>
+      <c r="O19">
+        <v>287838.05</v>
+      </c>
+      <c r="R19" t="s">
+        <v>115</v>
+      </c>
+      <c r="S19">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T19">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="s">
+        <v>121</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>2025</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20">
+        <v>525</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" s="2">
+        <v>45916.95960697917</v>
+      </c>
+      <c r="K20" t="s">
+        <v>106</v>
+      </c>
+      <c r="L20">
+        <v>-0.03039960648148148</v>
+      </c>
+      <c r="M20">
+        <v>-2626.526</v>
+      </c>
+      <c r="N20">
+        <v>2.5429403125</v>
+      </c>
+      <c r="O20">
+        <v>219710.043</v>
+      </c>
+      <c r="R20" t="s">
+        <v>119</v>
+      </c>
+      <c r="S20">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="T20">
+        <v>3.395833333333333</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="s">
+        <v>121</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21">
+        <v>2025</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21">
+        <v>308</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" s="2">
+        <v>45915.6401268287</v>
+      </c>
+      <c r="K21" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21">
+        <v>-0.0001284259259259259</v>
+      </c>
+      <c r="M21">
+        <v>-11.096</v>
+      </c>
+      <c r="N21">
+        <v>1.223460162037037</v>
+      </c>
+      <c r="O21">
+        <v>105706.958</v>
+      </c>
+      <c r="R21" t="s">
+        <v>117</v>
+      </c>
+      <c r="S21">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T21">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="s">
+        <v>121</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>2025</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22">
+        <v>355</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2">
+        <v>45916.44111702546</v>
+      </c>
+      <c r="K22" t="s">
+        <v>103</v>
+      </c>
+      <c r="L22">
+        <v>-0.0004208796296296296</v>
+      </c>
+      <c r="M22">
+        <v>-36.364</v>
+      </c>
+      <c r="N22">
+        <v>2.024450358796296</v>
+      </c>
+      <c r="O22">
+        <v>174912.511</v>
+      </c>
+      <c r="R22" t="s">
+        <v>118</v>
+      </c>
+      <c r="S22">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T22">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
+        <v>121</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23">
+        <v>2025</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23">
+        <v>384</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" t="s">
+        <v>100</v>
+      </c>
+      <c r="J23" s="2">
+        <v>45916.45647189815</v>
+      </c>
+      <c r="K23" t="s">
+        <v>107</v>
+      </c>
+      <c r="L23">
+        <v>-0.002893287037037037</v>
+      </c>
+      <c r="M23">
+        <v>-249.98</v>
+      </c>
+      <c r="N23">
+        <v>2.039805231481481</v>
+      </c>
+      <c r="O23">
+        <v>176239.172</v>
+      </c>
+      <c r="R23" t="s">
+        <v>118</v>
+      </c>
+      <c r="S23">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T23">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>2025</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24">
+        <v>546</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" s="2">
+        <v>45918.5644958912</v>
+      </c>
+      <c r="K24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L24">
+        <v>-0.9004283333333334</v>
+      </c>
+      <c r="M24">
+        <v>-77797.008</v>
+      </c>
+      <c r="N24">
+        <v>4.147829224537037</v>
+      </c>
+      <c r="O24">
+        <v>358372.445</v>
+      </c>
+      <c r="R24" t="s">
+        <v>113</v>
+      </c>
+      <c r="S24">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T24">
+        <v>5.375</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
+        <v>121</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>2025</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25">
+        <v>1096</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="2">
+        <v>45919.6443719213</v>
+      </c>
+      <c r="K25" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25">
+        <v>-0.03591431712962963</v>
+      </c>
+      <c r="M25">
+        <v>-3102.997</v>
+      </c>
+      <c r="N25">
+        <v>5.144371921296297</v>
+      </c>
+      <c r="O25">
+        <v>444473.734</v>
+      </c>
+      <c r="R25" t="s">
+        <v>113</v>
+      </c>
+      <c r="S25">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T25">
+        <v>5.375</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="s">
+        <v>121</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>2025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26">
+        <v>1070</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" t="s">
+        <v>97</v>
+      </c>
+      <c r="J26" s="2">
+        <v>45918.63040311343</v>
+      </c>
+      <c r="K26" t="s">
+        <v>107</v>
+      </c>
+      <c r="L26">
+        <v>-0.001639907407407407</v>
+      </c>
+      <c r="M26">
+        <v>-141.688</v>
+      </c>
+      <c r="N26">
+        <v>4.130403113425926</v>
+      </c>
+      <c r="O26">
+        <v>356866.829</v>
+      </c>
+      <c r="R26" t="s">
+        <v>115</v>
+      </c>
+      <c r="S26">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T26">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
+        <v>121</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>2025</v>
+      </c>
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27">
+        <v>651</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" t="s">
+        <v>97</v>
+      </c>
+      <c r="J27" s="2">
+        <v>45918.57802502315</v>
+      </c>
+      <c r="K27" t="s">
+        <v>107</v>
+      </c>
+      <c r="L27">
+        <v>-0.0001042708333333333</v>
+      </c>
+      <c r="M27">
+        <v>-9.009</v>
+      </c>
+      <c r="N27">
+        <v>4.161358356481482</v>
+      </c>
+      <c r="O27">
+        <v>359541.362</v>
+      </c>
+      <c r="R27" t="s">
+        <v>115</v>
+      </c>
+      <c r="S27">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T27">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
+        <v>121</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>2025</v>
+      </c>
+      <c r="C28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28">
+        <v>1190</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" t="s">
+        <v>97</v>
+      </c>
+      <c r="J28" s="2">
+        <v>45918.76002306713</v>
+      </c>
+      <c r="K28" t="s">
+        <v>111</v>
+      </c>
+      <c r="L28">
+        <v>-0.001359502314814815</v>
+      </c>
+      <c r="M28">
+        <v>-117.461</v>
+      </c>
+      <c r="N28">
+        <v>4.26002306712963</v>
+      </c>
+      <c r="O28">
+        <v>368065.993</v>
+      </c>
+      <c r="R28" t="s">
+        <v>115</v>
+      </c>
+      <c r="S28">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T28">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="s">
+        <v>121</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>2025</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29">
+        <v>95</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29" s="2">
+        <v>45915.49003822917</v>
+      </c>
+      <c r="K29" t="s">
+        <v>86</v>
+      </c>
+      <c r="L29">
+        <v>-0.1975464930555555</v>
+      </c>
+      <c r="M29">
+        <v>-17068.017</v>
+      </c>
+      <c r="N29">
+        <v>1.0733715625</v>
+      </c>
+      <c r="O29">
+        <v>92739.303</v>
+      </c>
+      <c r="P29" t="s">
+        <v>88</v>
+      </c>
+      <c r="R29" t="s">
+        <v>117</v>
+      </c>
+      <c r="S29">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T29">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="s">
+        <v>121</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30">
+        <v>2025</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30">
+        <v>403</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" t="s">
+        <v>102</v>
+      </c>
+      <c r="J30" s="2">
+        <v>45914.98248302083</v>
+      </c>
+      <c r="K30" t="s">
+        <v>86</v>
+      </c>
+      <c r="L30">
+        <v>-0.0498675925925926</v>
+      </c>
+      <c r="M30">
+        <v>-4308.56</v>
+      </c>
+      <c r="N30">
+        <v>0.5658163541666668</v>
+      </c>
+      <c r="O30">
+        <v>48886.533</v>
+      </c>
+      <c r="P30" t="s">
+        <v>102</v>
+      </c>
+      <c r="R30" t="s">
+        <v>120</v>
+      </c>
+      <c r="S30">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T30">
+        <v>0.875</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="s">
+        <v>121</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31">
+        <v>2025</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31">
+        <v>656</v>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="2">
+        <v>45915.42726980324</v>
+      </c>
+      <c r="K31" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31">
+        <v>-0.0001183796296296296</v>
+      </c>
+      <c r="M31">
+        <v>-10.228</v>
+      </c>
+      <c r="N31">
+        <v>1.010603136574074</v>
+      </c>
+      <c r="O31">
+        <v>87316.111</v>
+      </c>
+      <c r="P31" t="s">
+        <v>112</v>
+      </c>
+      <c r="R31" t="s">
+        <v>118</v>
+      </c>
+      <c r="S31">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T31">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
+        <v>121</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32">
+        <v>2025</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32">
+        <v>661</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" t="s">
+        <v>89</v>
+      </c>
+      <c r="H32" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" t="s">
+        <v>102</v>
+      </c>
+      <c r="J32" s="2">
+        <v>45915.19124746528</v>
+      </c>
+      <c r="K32" t="s">
+        <v>86</v>
+      </c>
+      <c r="L32">
+        <v>-0.1664284259259259</v>
+      </c>
+      <c r="M32">
+        <v>-14379.416</v>
+      </c>
+      <c r="N32">
+        <v>0.7745807986111112</v>
+      </c>
+      <c r="O32">
+        <v>66923.781</v>
+      </c>
+      <c r="P32" t="s">
+        <v>102</v>
+      </c>
+      <c r="R32" t="s">
+        <v>120</v>
+      </c>
+      <c r="S32">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T32">
+        <v>0.875</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="s">
+        <v>121</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33">
+        <v>2025</v>
+      </c>
+      <c r="C33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33">
+        <v>1131</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>86</v>
+      </c>
+      <c r="G33" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I33" t="s">
+        <v>102</v>
+      </c>
+      <c r="J33" s="2">
+        <v>45915.14697456019</v>
+      </c>
+      <c r="K33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L33">
+        <v>-0.04587693287037037</v>
+      </c>
+      <c r="M33">
+        <v>-3963.767</v>
+      </c>
+      <c r="N33">
+        <v>0.6469745601851852</v>
+      </c>
+      <c r="O33">
+        <v>55898.602</v>
+      </c>
+      <c r="P33" t="s">
+        <v>102</v>
+      </c>
+      <c r="R33" t="s">
+        <v>120</v>
+      </c>
+      <c r="S33">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T33">
+        <v>0.875</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="s">
+        <v>121</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34">
+        <v>2025</v>
+      </c>
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34">
+        <v>1187</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" t="s">
+        <v>89</v>
+      </c>
+      <c r="H34" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="2">
+        <v>45915.20803805556</v>
+      </c>
+      <c r="K34" t="s">
+        <v>86</v>
+      </c>
+      <c r="L34">
+        <v>-0.0543519212962963</v>
+      </c>
+      <c r="M34">
+        <v>-4696.006</v>
+      </c>
+      <c r="N34">
+        <v>0.7080380555555555</v>
+      </c>
+      <c r="O34">
+        <v>61174.488</v>
+      </c>
+      <c r="P34" t="s">
+        <v>102</v>
+      </c>
+      <c r="R34" t="s">
+        <v>120</v>
+      </c>
+      <c r="S34">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T34">
+        <v>0.875</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
+        <v>121</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35">
+        <v>2025</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35">
+        <v>1415</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="2">
+        <v>45917.80574773148</v>
+      </c>
+      <c r="K35" t="s">
+        <v>86</v>
+      </c>
+      <c r="L35">
+        <v>-0.02553084490740741</v>
+      </c>
+      <c r="M35">
+        <v>-2205.865</v>
+      </c>
+      <c r="N35">
+        <v>3.305747731481481</v>
+      </c>
+      <c r="O35">
+        <v>285616.604</v>
+      </c>
+      <c r="P35" t="s">
+        <v>91</v>
+      </c>
+      <c r="R35" t="s">
+        <v>114</v>
+      </c>
+      <c r="S35">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T35">
+        <v>3.625</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="s">
+        <v>121</v>
+      </c>
+      <c r="W35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36">
+        <v>2025</v>
+      </c>
+      <c r="C36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36">
+        <v>1497</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" t="s">
+        <v>89</v>
+      </c>
+      <c r="H36" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="2">
+        <v>45915.15566939815</v>
+      </c>
+      <c r="K36" t="s">
+        <v>86</v>
+      </c>
+      <c r="L36">
+        <v>-0.1091181712962963</v>
+      </c>
+      <c r="M36">
+        <v>-9427.809999999999</v>
+      </c>
+      <c r="N36">
+        <v>0.6556693981481482</v>
+      </c>
+      <c r="O36">
+        <v>56649.836</v>
+      </c>
+      <c r="P36" t="s">
+        <v>102</v>
+      </c>
+      <c r="R36" t="s">
+        <v>120</v>
+      </c>
+      <c r="S36">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T36">
+        <v>0.875</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="s">
+        <v>121</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>2025</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37">
+        <v>12</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" t="s">
+        <v>100</v>
+      </c>
+      <c r="J37" s="2">
+        <v>45915.42967841435</v>
+      </c>
+      <c r="K37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L37">
+        <v>-0.001164791666666667</v>
+      </c>
+      <c r="M37">
+        <v>-100.638</v>
+      </c>
+      <c r="N37">
+        <v>1.013011747685185</v>
+      </c>
+      <c r="O37">
+        <v>87524.215</v>
+      </c>
+      <c r="R37" t="s">
+        <v>118</v>
+      </c>
+      <c r="S37">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T37">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="s">
+        <v>121</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38">
+        <v>2025</v>
+      </c>
+      <c r="C38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38">
+        <v>7</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38" s="2">
+        <v>45915.14942453703</v>
+      </c>
+      <c r="K38" t="s">
+        <v>109</v>
+      </c>
+      <c r="L38">
+        <v>-0.0001758796296296296</v>
+      </c>
+      <c r="M38">
+        <v>-15.196</v>
+      </c>
+      <c r="N38">
+        <v>0.7327578703703703</v>
+      </c>
+      <c r="O38">
+        <v>63310.28</v>
+      </c>
+      <c r="R38" t="s">
+        <v>117</v>
+      </c>
+      <c r="S38">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T38">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="s">
+        <v>121</v>
+      </c>
+      <c r="W38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <v>2025</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39">
+        <v>54</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" s="2">
+        <v>45916.01724591435</v>
+      </c>
+      <c r="K39" t="s">
+        <v>110</v>
+      </c>
+      <c r="L39">
+        <v>-0.0004433912037037037</v>
+      </c>
+      <c r="M39">
+        <v>-38.309</v>
+      </c>
+      <c r="N39">
+        <v>1.600579247685185</v>
+      </c>
+      <c r="O39">
+        <v>138290.047</v>
+      </c>
+      <c r="R39" t="s">
+        <v>118</v>
+      </c>
+      <c r="S39">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T39">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="s">
+        <v>121</v>
+      </c>
+      <c r="W39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40">
+        <v>2025</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40">
+        <v>638</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" t="s">
+        <v>93</v>
+      </c>
+      <c r="I40" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40" s="2">
+        <v>45917.74812557871</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>-0.002106851851851852</v>
+      </c>
+      <c r="M40">
+        <v>-182.032</v>
+      </c>
+      <c r="N40">
+        <v>3.331458912037037</v>
+      </c>
+      <c r="O40">
+        <v>287838.05</v>
+      </c>
+      <c r="R40" t="s">
+        <v>115</v>
+      </c>
+      <c r="S40">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T40">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="s">
+        <v>121</v>
+      </c>
+      <c r="W40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41">
+        <v>2025</v>
+      </c>
+      <c r="C41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41">
+        <v>525</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="2">
+        <v>45916.95960697917</v>
+      </c>
+      <c r="K41" t="s">
+        <v>106</v>
+      </c>
+      <c r="L41">
+        <v>-0.03039960648148148</v>
+      </c>
+      <c r="M41">
+        <v>-2626.526</v>
+      </c>
+      <c r="N41">
+        <v>2.5429403125</v>
+      </c>
+      <c r="O41">
+        <v>219710.043</v>
+      </c>
+      <c r="R41" t="s">
+        <v>119</v>
+      </c>
+      <c r="S41">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="T41">
+        <v>3.395833333333333</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+      <c r="V41" t="s">
+        <v>121</v>
+      </c>
+      <c r="W41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42">
+        <v>2025</v>
+      </c>
+      <c r="C42" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42">
+        <v>308</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" t="s">
+        <v>93</v>
+      </c>
+      <c r="I42" t="s">
+        <v>99</v>
+      </c>
+      <c r="J42" s="2">
+        <v>45915.6401268287</v>
+      </c>
+      <c r="K42" t="s">
+        <v>106</v>
+      </c>
+      <c r="L42">
+        <v>-0.0001284259259259259</v>
+      </c>
+      <c r="M42">
+        <v>-11.096</v>
+      </c>
+      <c r="N42">
+        <v>1.223460162037037</v>
+      </c>
+      <c r="O42">
+        <v>105706.958</v>
+      </c>
+      <c r="R42" t="s">
+        <v>117</v>
+      </c>
+      <c r="S42">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T42">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="s">
+        <v>121</v>
+      </c>
+      <c r="W42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43">
+        <v>2025</v>
+      </c>
+      <c r="C43" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43">
+        <v>355</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" t="s">
+        <v>100</v>
+      </c>
+      <c r="J43" s="2">
+        <v>45916.44111702546</v>
+      </c>
+      <c r="K43" t="s">
+        <v>103</v>
+      </c>
+      <c r="L43">
+        <v>-0.0004208796296296296</v>
+      </c>
+      <c r="M43">
+        <v>-36.364</v>
+      </c>
+      <c r="N43">
+        <v>2.024450358796296</v>
+      </c>
+      <c r="O43">
+        <v>174912.511</v>
+      </c>
+      <c r="R43" t="s">
+        <v>118</v>
+      </c>
+      <c r="S43">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T43">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="s">
+        <v>121</v>
+      </c>
+      <c r="W43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>2025</v>
+      </c>
+      <c r="C44" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44">
+        <v>384</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" t="s">
+        <v>100</v>
+      </c>
+      <c r="J44" s="2">
+        <v>45916.45647189815</v>
+      </c>
+      <c r="K44" t="s">
+        <v>107</v>
+      </c>
+      <c r="L44">
+        <v>-0.002893287037037037</v>
+      </c>
+      <c r="M44">
+        <v>-249.98</v>
+      </c>
+      <c r="N44">
+        <v>2.039805231481481</v>
+      </c>
+      <c r="O44">
+        <v>176239.172</v>
+      </c>
+      <c r="R44" t="s">
+        <v>118</v>
+      </c>
+      <c r="S44">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T44">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
+        <v>121</v>
+      </c>
+      <c r="W44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>2025</v>
+      </c>
+      <c r="C45" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45">
+        <v>546</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" t="s">
+        <v>95</v>
+      </c>
+      <c r="J45" s="2">
+        <v>45918.5644958912</v>
+      </c>
+      <c r="K45" t="s">
+        <v>107</v>
+      </c>
+      <c r="L45">
+        <v>-0.9004283333333334</v>
+      </c>
+      <c r="M45">
+        <v>-77797.008</v>
+      </c>
+      <c r="N45">
+        <v>4.147829224537037</v>
+      </c>
+      <c r="O45">
+        <v>358372.445</v>
+      </c>
+      <c r="R45" t="s">
+        <v>113</v>
+      </c>
+      <c r="S45">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T45">
+        <v>5.375</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
+        <v>121</v>
+      </c>
+      <c r="W45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46">
+        <v>2025</v>
+      </c>
+      <c r="C46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46">
+        <v>1096</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" t="s">
+        <v>95</v>
+      </c>
+      <c r="J46" s="2">
+        <v>45919.6443719213</v>
+      </c>
+      <c r="K46" t="s">
+        <v>107</v>
+      </c>
+      <c r="L46">
+        <v>-0.03591431712962963</v>
+      </c>
+      <c r="M46">
+        <v>-3102.997</v>
+      </c>
+      <c r="N46">
+        <v>5.144371921296297</v>
+      </c>
+      <c r="O46">
+        <v>444473.734</v>
+      </c>
+      <c r="R46" t="s">
+        <v>113</v>
+      </c>
+      <c r="S46">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T46">
+        <v>5.375</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
+        <v>121</v>
+      </c>
+      <c r="W46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <v>2025</v>
+      </c>
+      <c r="C47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47">
+        <v>1070</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" t="s">
+        <v>94</v>
+      </c>
+      <c r="I47" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" s="2">
+        <v>45918.63040311343</v>
+      </c>
+      <c r="K47" t="s">
+        <v>107</v>
+      </c>
+      <c r="L47">
+        <v>-0.001639907407407407</v>
+      </c>
+      <c r="M47">
+        <v>-141.688</v>
+      </c>
+      <c r="N47">
+        <v>4.130403113425926</v>
+      </c>
+      <c r="O47">
+        <v>356866.829</v>
+      </c>
+      <c r="R47" t="s">
+        <v>115</v>
+      </c>
+      <c r="S47">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T47">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
+        <v>121</v>
+      </c>
+      <c r="W47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48">
+        <v>2025</v>
+      </c>
+      <c r="C48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48">
+        <v>651</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48" t="s">
+        <v>93</v>
+      </c>
+      <c r="I48" t="s">
+        <v>97</v>
+      </c>
+      <c r="J48" s="2">
+        <v>45918.57802502315</v>
+      </c>
+      <c r="K48" t="s">
+        <v>107</v>
+      </c>
+      <c r="L48">
+        <v>-0.0001042708333333333</v>
+      </c>
+      <c r="M48">
+        <v>-9.009</v>
+      </c>
+      <c r="N48">
+        <v>4.161358356481482</v>
+      </c>
+      <c r="O48">
+        <v>359541.362</v>
+      </c>
+      <c r="R48" t="s">
+        <v>115</v>
+      </c>
+      <c r="S48">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T48">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" t="s">
+        <v>121</v>
+      </c>
+      <c r="W48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49">
+        <v>2025</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49">
+        <v>1190</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" t="s">
+        <v>94</v>
+      </c>
+      <c r="I49" t="s">
+        <v>97</v>
+      </c>
+      <c r="J49" s="2">
+        <v>45918.76002306713</v>
+      </c>
+      <c r="K49" t="s">
+        <v>111</v>
+      </c>
+      <c r="L49">
+        <v>-0.001359502314814815</v>
+      </c>
+      <c r="M49">
+        <v>-117.461</v>
+      </c>
+      <c r="N49">
+        <v>4.26002306712963</v>
+      </c>
+      <c r="O49">
+        <v>368065.993</v>
+      </c>
+      <c r="R49" t="s">
+        <v>115</v>
+      </c>
+      <c r="S49">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T49">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="s">
+        <v>121</v>
+      </c>
+      <c r="W49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>2025</v>
+      </c>
+      <c r="C50" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50">
+        <v>95</v>
+      </c>
+      <c r="E50" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G50" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s">
+        <v>93</v>
+      </c>
+      <c r="I50" t="s">
+        <v>99</v>
+      </c>
+      <c r="J50" s="2">
+        <v>45915.49003822917</v>
+      </c>
+      <c r="K50" t="s">
+        <v>86</v>
+      </c>
+      <c r="L50">
+        <v>-0.1975464930555555</v>
+      </c>
+      <c r="M50">
+        <v>-17068.017</v>
+      </c>
+      <c r="N50">
+        <v>1.0733715625</v>
+      </c>
+      <c r="O50">
+        <v>92739.303</v>
+      </c>
+      <c r="P50" t="s">
+        <v>88</v>
+      </c>
+      <c r="R50" t="s">
+        <v>117</v>
+      </c>
+      <c r="S50">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T50">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
+        <v>121</v>
+      </c>
+      <c r="W50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2025</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51">
+        <v>403</v>
+      </c>
+      <c r="E51" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
+        <v>86</v>
+      </c>
+      <c r="G51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s">
+        <v>93</v>
+      </c>
+      <c r="I51" t="s">
+        <v>102</v>
+      </c>
+      <c r="J51" s="2">
+        <v>45914.98248302083</v>
+      </c>
+      <c r="K51" t="s">
+        <v>86</v>
+      </c>
+      <c r="L51">
+        <v>-0.0498675925925926</v>
+      </c>
+      <c r="M51">
+        <v>-4308.56</v>
+      </c>
+      <c r="N51">
+        <v>0.5658163541666668</v>
+      </c>
+      <c r="O51">
+        <v>48886.533</v>
+      </c>
+      <c r="P51" t="s">
+        <v>102</v>
+      </c>
+      <c r="R51" t="s">
+        <v>120</v>
+      </c>
+      <c r="S51">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T51">
+        <v>0.875</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+      <c r="V51" t="s">
+        <v>121</v>
+      </c>
+      <c r="W51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2025</v>
+      </c>
+      <c r="C52" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52">
+        <v>656</v>
+      </c>
+      <c r="E52" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" t="s">
+        <v>86</v>
+      </c>
+      <c r="G52" t="s">
+        <v>90</v>
+      </c>
+      <c r="H52" t="s">
+        <v>93</v>
+      </c>
+      <c r="I52" t="s">
+        <v>100</v>
+      </c>
+      <c r="J52" s="2">
+        <v>45915.42726980324</v>
+      </c>
+      <c r="K52" t="s">
+        <v>86</v>
+      </c>
+      <c r="L52">
+        <v>-0.0001183796296296296</v>
+      </c>
+      <c r="M52">
+        <v>-10.228</v>
+      </c>
+      <c r="N52">
+        <v>1.010603136574074</v>
+      </c>
+      <c r="O52">
+        <v>87316.111</v>
+      </c>
+      <c r="P52" t="s">
+        <v>112</v>
+      </c>
+      <c r="R52" t="s">
+        <v>118</v>
+      </c>
+      <c r="S52">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T52">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+      <c r="V52" t="s">
+        <v>121</v>
+      </c>
+      <c r="W52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>2025</v>
+      </c>
+      <c r="C53" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53">
+        <v>661</v>
+      </c>
+      <c r="E53" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>86</v>
+      </c>
+      <c r="G53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s">
+        <v>93</v>
+      </c>
+      <c r="I53" t="s">
+        <v>102</v>
+      </c>
+      <c r="J53" s="2">
+        <v>45915.19124746528</v>
+      </c>
+      <c r="K53" t="s">
+        <v>86</v>
+      </c>
+      <c r="L53">
+        <v>-0.1664284259259259</v>
+      </c>
+      <c r="M53">
+        <v>-14379.416</v>
+      </c>
+      <c r="N53">
+        <v>0.7745807986111112</v>
+      </c>
+      <c r="O53">
+        <v>66923.781</v>
+      </c>
+      <c r="P53" t="s">
+        <v>102</v>
+      </c>
+      <c r="R53" t="s">
+        <v>120</v>
+      </c>
+      <c r="S53">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T53">
+        <v>0.875</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+      <c r="V53" t="s">
+        <v>121</v>
+      </c>
+      <c r="W53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>2025</v>
+      </c>
+      <c r="C54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54">
+        <v>1131</v>
+      </c>
+      <c r="E54" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>86</v>
+      </c>
+      <c r="G54" t="s">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s">
+        <v>94</v>
+      </c>
+      <c r="I54" t="s">
+        <v>102</v>
+      </c>
+      <c r="J54" s="2">
+        <v>45915.14697456019</v>
+      </c>
+      <c r="K54" t="s">
+        <v>86</v>
+      </c>
+      <c r="L54">
+        <v>-0.04587693287037037</v>
+      </c>
+      <c r="M54">
+        <v>-3963.767</v>
+      </c>
+      <c r="N54">
+        <v>0.6469745601851852</v>
+      </c>
+      <c r="O54">
+        <v>55898.602</v>
+      </c>
+      <c r="P54" t="s">
+        <v>102</v>
+      </c>
+      <c r="R54" t="s">
+        <v>120</v>
+      </c>
+      <c r="S54">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T54">
+        <v>0.875</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
+        <v>121</v>
+      </c>
+      <c r="W54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55">
+        <v>2025</v>
+      </c>
+      <c r="C55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D55">
+        <v>1187</v>
+      </c>
+      <c r="E55" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G55" t="s">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s">
+        <v>94</v>
+      </c>
+      <c r="I55" t="s">
+        <v>102</v>
+      </c>
+      <c r="J55" s="2">
+        <v>45915.20803805556</v>
+      </c>
+      <c r="K55" t="s">
+        <v>86</v>
+      </c>
+      <c r="L55">
+        <v>-0.0543519212962963</v>
+      </c>
+      <c r="M55">
+        <v>-4696.006</v>
+      </c>
+      <c r="N55">
+        <v>0.7080380555555555</v>
+      </c>
+      <c r="O55">
+        <v>61174.488</v>
+      </c>
+      <c r="P55" t="s">
+        <v>102</v>
+      </c>
+      <c r="R55" t="s">
+        <v>120</v>
+      </c>
+      <c r="S55">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T55">
+        <v>0.875</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
+        <v>121</v>
+      </c>
+      <c r="W55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56">
+        <v>2025</v>
+      </c>
+      <c r="C56" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56">
+        <v>1415</v>
+      </c>
+      <c r="E56" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>86</v>
+      </c>
+      <c r="G56" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" t="s">
+        <v>96</v>
+      </c>
+      <c r="J56" s="2">
+        <v>45917.80574773148</v>
+      </c>
+      <c r="K56" t="s">
+        <v>86</v>
+      </c>
+      <c r="L56">
+        <v>-0.02553084490740741</v>
+      </c>
+      <c r="M56">
+        <v>-2205.865</v>
+      </c>
+      <c r="N56">
+        <v>3.305747731481481</v>
+      </c>
+      <c r="O56">
+        <v>285616.604</v>
+      </c>
+      <c r="P56" t="s">
+        <v>91</v>
+      </c>
+      <c r="R56" t="s">
+        <v>114</v>
+      </c>
+      <c r="S56">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T56">
+        <v>3.625</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
+        <v>121</v>
+      </c>
+      <c r="W56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57">
+        <v>2025</v>
+      </c>
+      <c r="C57" t="s">
+        <v>61</v>
+      </c>
+      <c r="D57">
+        <v>1497</v>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>86</v>
+      </c>
+      <c r="G57" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s">
+        <v>94</v>
+      </c>
+      <c r="I57" t="s">
+        <v>102</v>
+      </c>
+      <c r="J57" s="2">
+        <v>45915.15566939815</v>
+      </c>
+      <c r="K57" t="s">
+        <v>86</v>
+      </c>
+      <c r="L57">
+        <v>-0.1091181712962963</v>
+      </c>
+      <c r="M57">
+        <v>-9427.809999999999</v>
+      </c>
+      <c r="N57">
+        <v>0.6556693981481482</v>
+      </c>
+      <c r="O57">
+        <v>56649.836</v>
+      </c>
+      <c r="P57" t="s">
+        <v>102</v>
+      </c>
+      <c r="R57" t="s">
+        <v>120</v>
+      </c>
+      <c r="S57">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T57">
+        <v>0.875</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+      <c r="V57" t="s">
+        <v>121</v>
+      </c>
+      <c r="W57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58">
+        <v>2023</v>
+      </c>
+      <c r="C58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58">
+        <v>334</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58" t="s">
+        <v>93</v>
+      </c>
+      <c r="I58" t="s">
+        <v>98</v>
+      </c>
+      <c r="J58" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K58" t="s">
+        <v>106</v>
+      </c>
+      <c r="L58">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M58">
+        <v>-4927</v>
+      </c>
+      <c r="N58">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O58">
+        <v>128649</v>
+      </c>
+      <c r="R58" t="s">
+        <v>116</v>
+      </c>
+      <c r="S58">
+        <v>0.75</v>
+      </c>
+      <c r="T58">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
+        <v>121</v>
+      </c>
+      <c r="W58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59">
+        <v>2023</v>
+      </c>
+      <c r="C59" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59">
+        <v>343</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s">
+        <v>93</v>
+      </c>
+      <c r="I59" t="s">
+        <v>96</v>
+      </c>
+      <c r="J59" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K59" t="s">
+        <v>103</v>
+      </c>
+      <c r="L59">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M59">
+        <v>-34</v>
+      </c>
+      <c r="N59">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O59">
+        <v>263346</v>
+      </c>
+      <c r="R59" t="s">
+        <v>114</v>
+      </c>
+      <c r="S59">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T59">
+        <v>3.625</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+      <c r="V59" t="s">
+        <v>121</v>
+      </c>
+      <c r="W59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60">
+        <v>2023</v>
+      </c>
+      <c r="C60" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60">
+        <v>1291</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" t="s">
+        <v>99</v>
+      </c>
+      <c r="J60" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K60" t="s">
+        <v>107</v>
+      </c>
+      <c r="L60">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M60">
+        <v>-10</v>
+      </c>
+      <c r="N60">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O60">
+        <v>125684</v>
+      </c>
+      <c r="R60" t="s">
+        <v>117</v>
+      </c>
+      <c r="S60">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T60">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+      <c r="V60" t="s">
+        <v>121</v>
+      </c>
+      <c r="W60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61">
+        <v>2023</v>
+      </c>
+      <c r="C61" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61">
+        <v>423</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>83</v>
+      </c>
+      <c r="H61" t="s">
+        <v>93</v>
+      </c>
+      <c r="I61" t="s">
+        <v>95</v>
+      </c>
+      <c r="J61" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K61" t="s">
+        <v>107</v>
+      </c>
+      <c r="L61">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M61">
+        <v>-2151</v>
+      </c>
+      <c r="N61">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O61">
+        <v>382577</v>
+      </c>
+      <c r="R61" t="s">
+        <v>113</v>
+      </c>
+      <c r="S61">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T61">
+        <v>5.375</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+      <c r="V61" t="s">
+        <v>121</v>
+      </c>
+      <c r="W61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62">
+        <v>2023</v>
+      </c>
+      <c r="C62" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62">
+        <v>1334</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s">
+        <v>94</v>
+      </c>
+      <c r="I62" t="s">
+        <v>99</v>
+      </c>
+      <c r="J62" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K62" t="s">
+        <v>107</v>
+      </c>
+      <c r="L62">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M62">
+        <v>-18</v>
+      </c>
+      <c r="N62">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O62">
+        <v>128141</v>
+      </c>
+      <c r="R62" t="s">
+        <v>117</v>
+      </c>
+      <c r="S62">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T62">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U62" t="b">
+        <v>0</v>
+      </c>
+      <c r="V62" t="s">
+        <v>121</v>
+      </c>
+      <c r="W62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63">
+        <v>2023</v>
+      </c>
+      <c r="C63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63">
+        <v>334</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s">
+        <v>93</v>
+      </c>
+      <c r="I63" t="s">
+        <v>98</v>
+      </c>
+      <c r="J63" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K63" t="s">
+        <v>106</v>
+      </c>
+      <c r="L63">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M63">
+        <v>-4927</v>
+      </c>
+      <c r="N63">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O63">
+        <v>128649</v>
+      </c>
+      <c r="R63" t="s">
+        <v>116</v>
+      </c>
+      <c r="S63">
+        <v>0.75</v>
+      </c>
+      <c r="T63">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U63" t="b">
+        <v>0</v>
+      </c>
+      <c r="V63" t="s">
+        <v>121</v>
+      </c>
+      <c r="W63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64">
+        <v>2023</v>
+      </c>
+      <c r="C64" t="s">
+        <v>61</v>
+      </c>
+      <c r="D64">
+        <v>343</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s">
+        <v>93</v>
+      </c>
+      <c r="I64" t="s">
+        <v>96</v>
+      </c>
+      <c r="J64" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K64" t="s">
+        <v>103</v>
+      </c>
+      <c r="L64">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M64">
+        <v>-34</v>
+      </c>
+      <c r="N64">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O64">
+        <v>263346</v>
+      </c>
+      <c r="R64" t="s">
+        <v>114</v>
+      </c>
+      <c r="S64">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T64">
+        <v>3.625</v>
+      </c>
+      <c r="U64" t="b">
+        <v>0</v>
+      </c>
+      <c r="V64" t="s">
+        <v>121</v>
+      </c>
+      <c r="W64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="A65" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65">
+        <v>2023</v>
+      </c>
+      <c r="C65" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65">
+        <v>1291</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s">
+        <v>94</v>
+      </c>
+      <c r="I65" t="s">
+        <v>99</v>
+      </c>
+      <c r="J65" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K65" t="s">
+        <v>107</v>
+      </c>
+      <c r="L65">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M65">
+        <v>-10</v>
+      </c>
+      <c r="N65">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O65">
+        <v>125684</v>
+      </c>
+      <c r="R65" t="s">
+        <v>117</v>
+      </c>
+      <c r="S65">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T65">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U65" t="b">
+        <v>0</v>
+      </c>
+      <c r="V65" t="s">
+        <v>121</v>
+      </c>
+      <c r="W65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23">
+      <c r="A66" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66">
+        <v>2023</v>
+      </c>
+      <c r="C66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66">
+        <v>423</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s">
+        <v>93</v>
+      </c>
+      <c r="I66" t="s">
+        <v>95</v>
+      </c>
+      <c r="J66" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K66" t="s">
+        <v>107</v>
+      </c>
+      <c r="L66">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M66">
+        <v>-2151</v>
+      </c>
+      <c r="N66">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O66">
+        <v>382577</v>
+      </c>
+      <c r="R66" t="s">
+        <v>113</v>
+      </c>
+      <c r="S66">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T66">
+        <v>5.375</v>
+      </c>
+      <c r="U66" t="b">
+        <v>0</v>
+      </c>
+      <c r="V66" t="s">
+        <v>121</v>
+      </c>
+      <c r="W66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23">
+      <c r="A67" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67">
+        <v>2023</v>
+      </c>
+      <c r="C67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67">
+        <v>1334</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s">
+        <v>94</v>
+      </c>
+      <c r="I67" t="s">
+        <v>99</v>
+      </c>
+      <c r="J67" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K67" t="s">
+        <v>107</v>
+      </c>
+      <c r="L67">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M67">
+        <v>-18</v>
+      </c>
+      <c r="N67">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O67">
+        <v>128141</v>
+      </c>
+      <c r="R67" t="s">
+        <v>117</v>
+      </c>
+      <c r="S67">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T67">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U67" t="b">
+        <v>0</v>
+      </c>
+      <c r="V67" t="s">
+        <v>121</v>
+      </c>
+      <c r="W67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68">
+        <v>2021</v>
+      </c>
+      <c r="C68" t="s">
+        <v>61</v>
+      </c>
+      <c r="D68">
+        <v>162</v>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s">
+        <v>92</v>
+      </c>
+      <c r="I68" t="s">
+        <v>95</v>
+      </c>
+      <c r="J68" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K68" t="s">
+        <v>103</v>
+      </c>
+      <c r="L68">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M68">
+        <v>-88</v>
+      </c>
+      <c r="N68">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O68">
+        <v>415022</v>
+      </c>
+      <c r="R68" t="s">
+        <v>113</v>
+      </c>
+      <c r="S68">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T68">
+        <v>5.375</v>
+      </c>
+      <c r="U68" t="b">
+        <v>0</v>
+      </c>
+      <c r="V68" t="s">
+        <v>121</v>
+      </c>
+      <c r="W68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69">
+        <v>2021</v>
+      </c>
+      <c r="C69" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69">
+        <v>162</v>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s">
+        <v>92</v>
+      </c>
+      <c r="I69" t="s">
+        <v>95</v>
+      </c>
+      <c r="J69" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K69" t="s">
+        <v>103</v>
+      </c>
+      <c r="L69">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M69">
+        <v>-88</v>
+      </c>
+      <c r="N69">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O69">
+        <v>415022</v>
+      </c>
+      <c r="R69" t="s">
+        <v>113</v>
+      </c>
+      <c r="S69">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T69">
+        <v>5.375</v>
+      </c>
+      <c r="U69" t="b">
+        <v>0</v>
+      </c>
+      <c r="V69" t="s">
+        <v>121</v>
+      </c>
+      <c r="W69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23">
+      <c r="A70" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70" t="s">
+        <v>61</v>
+      </c>
+      <c r="D70">
+        <v>275</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>83</v>
+      </c>
+      <c r="H70" t="s">
+        <v>93</v>
+      </c>
+      <c r="I70" t="s">
+        <v>96</v>
+      </c>
+      <c r="J70" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K70" t="s">
+        <v>104</v>
+      </c>
+      <c r="L70">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M70">
+        <v>-281</v>
+      </c>
+      <c r="N70">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O70">
+        <v>170704</v>
+      </c>
+      <c r="R70" t="s">
+        <v>114</v>
+      </c>
+      <c r="S70">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T70">
+        <v>3.625</v>
+      </c>
+      <c r="U70" t="b">
+        <v>0</v>
+      </c>
+      <c r="V70" t="s">
+        <v>121</v>
+      </c>
+      <c r="W70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23">
+      <c r="A71" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71">
+        <v>2022</v>
+      </c>
+      <c r="C71" t="s">
+        <v>61</v>
+      </c>
+      <c r="D71">
+        <v>127</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s">
+        <v>93</v>
+      </c>
+      <c r="I71" t="s">
+        <v>97</v>
+      </c>
+      <c r="J71" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K71" t="s">
+        <v>105</v>
+      </c>
+      <c r="L71">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M71">
+        <v>-47</v>
+      </c>
+      <c r="N71">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O71">
+        <v>246403</v>
+      </c>
+      <c r="R71" t="s">
+        <v>115</v>
+      </c>
+      <c r="S71">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T71">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U71" t="b">
+        <v>0</v>
+      </c>
+      <c r="V71" t="s">
+        <v>121</v>
+      </c>
+      <c r="W71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72">
+        <v>2022</v>
+      </c>
+      <c r="C72" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72">
+        <v>549</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s">
+        <v>93</v>
+      </c>
+      <c r="I72" t="s">
+        <v>95</v>
+      </c>
+      <c r="J72" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K72" t="s">
+        <v>103</v>
+      </c>
+      <c r="L72">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M72">
+        <v>-31</v>
+      </c>
+      <c r="N72">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O72">
+        <v>418059</v>
+      </c>
+      <c r="R72" t="s">
+        <v>113</v>
+      </c>
+      <c r="S72">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T72">
+        <v>5.375</v>
+      </c>
+      <c r="U72" t="b">
+        <v>0</v>
+      </c>
+      <c r="V72" t="s">
+        <v>121</v>
+      </c>
+      <c r="W72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23">
+      <c r="A73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73">
+        <v>2022</v>
+      </c>
+      <c r="C73" t="s">
+        <v>61</v>
+      </c>
+      <c r="D73">
+        <v>1005</v>
+      </c>
+      <c r="E73" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>84</v>
+      </c>
+      <c r="H73" t="s">
+        <v>94</v>
+      </c>
+      <c r="I73" t="s">
+        <v>97</v>
+      </c>
+      <c r="J73" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L73">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M73">
+        <v>-24</v>
+      </c>
+      <c r="N73">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O73">
+        <v>346188</v>
+      </c>
+      <c r="R73" t="s">
+        <v>115</v>
+      </c>
+      <c r="S73">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T73">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U73" t="b">
+        <v>0</v>
+      </c>
+      <c r="V73" t="s">
+        <v>121</v>
+      </c>
+      <c r="W73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23">
+      <c r="A74" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74">
+        <v>2022</v>
+      </c>
+      <c r="C74" t="s">
+        <v>61</v>
+      </c>
+      <c r="D74">
+        <v>1205</v>
+      </c>
+      <c r="E74" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>85</v>
+      </c>
+      <c r="H74" t="s">
+        <v>94</v>
+      </c>
+      <c r="I74" t="s">
+        <v>96</v>
+      </c>
+      <c r="J74" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L74">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M74">
+        <v>-19</v>
+      </c>
+      <c r="N74">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O74">
+        <v>295845</v>
+      </c>
+      <c r="R74" t="s">
+        <v>114</v>
+      </c>
+      <c r="S74">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T74">
+        <v>3.625</v>
+      </c>
+      <c r="U74" t="b">
+        <v>0</v>
+      </c>
+      <c r="V74" t="s">
+        <v>121</v>
+      </c>
+      <c r="W74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23">
+      <c r="A75" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75">
+        <v>2022</v>
+      </c>
+      <c r="C75" t="s">
+        <v>61</v>
+      </c>
+      <c r="D75">
+        <v>1268</v>
+      </c>
+      <c r="E75" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>85</v>
+      </c>
+      <c r="H75" t="s">
+        <v>94</v>
+      </c>
+      <c r="I75" t="s">
+        <v>96</v>
+      </c>
+      <c r="J75" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L75">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M75">
+        <v>-72</v>
+      </c>
+      <c r="N75">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O75">
+        <v>295911</v>
+      </c>
+      <c r="R75" t="s">
+        <v>114</v>
+      </c>
+      <c r="S75">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T75">
+        <v>3.625</v>
+      </c>
+      <c r="U75" t="b">
+        <v>0</v>
+      </c>
+      <c r="V75" t="s">
+        <v>121</v>
+      </c>
+      <c r="W75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23">
+      <c r="A76" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76">
+        <v>2023</v>
+      </c>
+      <c r="C76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D76">
+        <v>334</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>83</v>
+      </c>
+      <c r="H76" t="s">
+        <v>93</v>
+      </c>
+      <c r="I76" t="s">
+        <v>98</v>
+      </c>
+      <c r="J76" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K76" t="s">
+        <v>106</v>
+      </c>
+      <c r="L76">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M76">
+        <v>-4927</v>
+      </c>
+      <c r="N76">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O76">
+        <v>128649</v>
+      </c>
+      <c r="R76" t="s">
+        <v>116</v>
+      </c>
+      <c r="S76">
+        <v>0.75</v>
+      </c>
+      <c r="T76">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="U76" t="b">
+        <v>0</v>
+      </c>
+      <c r="V76" t="s">
+        <v>121</v>
+      </c>
+      <c r="W76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23">
+      <c r="A77" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77">
+        <v>2023</v>
+      </c>
+      <c r="C77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77">
+        <v>343</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>83</v>
+      </c>
+      <c r="H77" t="s">
+        <v>93</v>
+      </c>
+      <c r="I77" t="s">
+        <v>96</v>
+      </c>
+      <c r="J77" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K77" t="s">
+        <v>103</v>
+      </c>
+      <c r="L77">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M77">
+        <v>-34</v>
+      </c>
+      <c r="N77">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O77">
+        <v>263346</v>
+      </c>
+      <c r="R77" t="s">
+        <v>114</v>
+      </c>
+      <c r="S77">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T77">
+        <v>3.625</v>
+      </c>
+      <c r="U77" t="b">
+        <v>0</v>
+      </c>
+      <c r="V77" t="s">
+        <v>121</v>
+      </c>
+      <c r="W77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23">
+      <c r="A78" t="s">
+        <v>34</v>
+      </c>
+      <c r="B78">
+        <v>2023</v>
+      </c>
+      <c r="C78" t="s">
+        <v>61</v>
+      </c>
+      <c r="D78">
+        <v>1291</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>83</v>
+      </c>
+      <c r="H78" t="s">
+        <v>94</v>
+      </c>
+      <c r="I78" t="s">
+        <v>99</v>
+      </c>
+      <c r="J78" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K78" t="s">
+        <v>107</v>
+      </c>
+      <c r="L78">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M78">
+        <v>-10</v>
+      </c>
+      <c r="N78">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O78">
+        <v>125684</v>
+      </c>
+      <c r="R78" t="s">
+        <v>117</v>
+      </c>
+      <c r="S78">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T78">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U78" t="b">
+        <v>0</v>
+      </c>
+      <c r="V78" t="s">
+        <v>121</v>
+      </c>
+      <c r="W78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23">
+      <c r="A79" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79">
+        <v>2023</v>
+      </c>
+      <c r="C79" t="s">
+        <v>61</v>
+      </c>
+      <c r="D79">
+        <v>423</v>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>83</v>
+      </c>
+      <c r="H79" t="s">
+        <v>93</v>
+      </c>
+      <c r="I79" t="s">
+        <v>95</v>
+      </c>
+      <c r="J79" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K79" t="s">
+        <v>107</v>
+      </c>
+      <c r="L79">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M79">
+        <v>-2151</v>
+      </c>
+      <c r="N79">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O79">
+        <v>382577</v>
+      </c>
+      <c r="R79" t="s">
+        <v>113</v>
+      </c>
+      <c r="S79">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T79">
+        <v>5.375</v>
+      </c>
+      <c r="U79" t="b">
+        <v>0</v>
+      </c>
+      <c r="V79" t="s">
+        <v>121</v>
+      </c>
+      <c r="W79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23">
+      <c r="A80" t="s">
+        <v>36</v>
+      </c>
+      <c r="B80">
+        <v>2023</v>
+      </c>
+      <c r="C80" t="s">
+        <v>61</v>
+      </c>
+      <c r="D80">
+        <v>1334</v>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>83</v>
+      </c>
+      <c r="H80" t="s">
+        <v>94</v>
+      </c>
+      <c r="I80" t="s">
+        <v>99</v>
+      </c>
+      <c r="J80" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K80" t="s">
+        <v>107</v>
+      </c>
+      <c r="L80">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M80">
+        <v>-18</v>
+      </c>
+      <c r="N80">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O80">
+        <v>128141</v>
+      </c>
+      <c r="R80" t="s">
+        <v>117</v>
+      </c>
+      <c r="S80">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T80">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U80" t="b">
+        <v>0</v>
+      </c>
+      <c r="V80" t="s">
+        <v>121</v>
+      </c>
+      <c r="W80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23">
+      <c r="A81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81">
+        <v>2024</v>
+      </c>
+      <c r="C81" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81">
+        <v>404</v>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>83</v>
+      </c>
+      <c r="H81" t="s">
+        <v>93</v>
+      </c>
+      <c r="I81" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K81" t="s">
+        <v>106</v>
+      </c>
+      <c r="L81">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M81">
+        <v>-651</v>
+      </c>
+      <c r="N81">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O81">
+        <v>290382</v>
+      </c>
+      <c r="R81" t="s">
+        <v>115</v>
+      </c>
+      <c r="S81">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T81">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U81" t="b">
+        <v>0</v>
+      </c>
+      <c r="V81" t="s">
+        <v>121</v>
+      </c>
+      <c r="W81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23">
+      <c r="A82" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82">
+        <v>2024</v>
+      </c>
+      <c r="C82" t="s">
+        <v>61</v>
+      </c>
+      <c r="D82">
+        <v>1367</v>
+      </c>
+      <c r="E82" t="b">
+        <v>0</v>
+      </c>
+      <c r="F82" t="s">
+        <v>86</v>
+      </c>
+      <c r="G82" t="s">
+        <v>87</v>
+      </c>
+      <c r="H82" t="s">
+        <v>94</v>
+      </c>
+      <c r="I82" t="s">
+        <v>99</v>
+      </c>
+      <c r="J82" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K82" t="s">
+        <v>86</v>
+      </c>
+      <c r="L82">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M82">
+        <v>-31</v>
+      </c>
+      <c r="N82">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O82">
+        <v>141955</v>
+      </c>
+      <c r="P82" t="s">
+        <v>99</v>
+      </c>
+      <c r="R82" t="s">
+        <v>117</v>
+      </c>
+      <c r="S82">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T82">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U82" t="b">
+        <v>0</v>
+      </c>
+      <c r="V82" t="s">
+        <v>121</v>
+      </c>
+      <c r="W82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" t="s">
+        <v>61</v>
+      </c>
+      <c r="D83" t="s">
+        <v>62</v>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>83</v>
+      </c>
+      <c r="H83" t="s">
+        <v>93</v>
+      </c>
+      <c r="I83" t="s">
+        <v>100</v>
+      </c>
+      <c r="J83" s="2">
+        <v>45915.42967841435</v>
+      </c>
+      <c r="K83" t="s">
+        <v>108</v>
+      </c>
+      <c r="L83" s="3">
+        <v>-0.001164791666666667</v>
+      </c>
+      <c r="M83">
+        <v>-100.638</v>
+      </c>
+      <c r="N83" s="3">
+        <v>1.013011747685185</v>
+      </c>
+      <c r="O83">
+        <v>87524.215</v>
+      </c>
+      <c r="R83" t="s">
+        <v>118</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T83" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U83" t="b">
+        <v>0</v>
+      </c>
+      <c r="V83" t="s">
+        <v>121</v>
+      </c>
+      <c r="W83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23">
+      <c r="A84" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" t="s">
+        <v>61</v>
+      </c>
+      <c r="D84" t="s">
+        <v>63</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>83</v>
+      </c>
+      <c r="H84" t="s">
+        <v>93</v>
+      </c>
+      <c r="I84" t="s">
+        <v>99</v>
+      </c>
+      <c r="J84" s="2">
+        <v>45915.14942453703</v>
+      </c>
+      <c r="K84" t="s">
+        <v>109</v>
+      </c>
+      <c r="L84" s="3">
+        <v>-0.0001758796296296296</v>
+      </c>
+      <c r="M84">
+        <v>-15.196</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0.7327578703703703</v>
+      </c>
+      <c r="O84">
+        <v>63310.28</v>
+      </c>
+      <c r="R84" t="s">
+        <v>117</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T84" s="3">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U84" t="b">
+        <v>0</v>
+      </c>
+      <c r="V84" t="s">
+        <v>121</v>
+      </c>
+      <c r="W84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23">
+      <c r="A85" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" t="s">
+        <v>60</v>
+      </c>
+      <c r="C85" t="s">
+        <v>61</v>
+      </c>
+      <c r="D85" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>83</v>
+      </c>
+      <c r="H85" t="s">
+        <v>93</v>
+      </c>
+      <c r="I85" t="s">
+        <v>100</v>
+      </c>
+      <c r="J85" s="2">
+        <v>45916.01724591435</v>
+      </c>
+      <c r="K85" t="s">
+        <v>110</v>
+      </c>
+      <c r="L85" s="3">
+        <v>-0.0004433912037037037</v>
+      </c>
+      <c r="M85">
+        <v>-38.309</v>
+      </c>
+      <c r="N85" s="3">
+        <v>1.600579247685185</v>
+      </c>
+      <c r="O85">
+        <v>138290.047</v>
+      </c>
+      <c r="R85" t="s">
+        <v>118</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T85" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U85" t="b">
+        <v>0</v>
+      </c>
+      <c r="V85" t="s">
+        <v>121</v>
+      </c>
+      <c r="W85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23">
+      <c r="A86" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86" t="s">
+        <v>61</v>
+      </c>
+      <c r="D86" t="s">
         <v>65</v>
       </c>
-      <c r="S15" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="s">
+        <v>83</v>
+      </c>
+      <c r="H86" t="s">
+        <v>93</v>
+      </c>
+      <c r="I86" t="s">
+        <v>97</v>
+      </c>
+      <c r="J86" s="2">
+        <v>45917.74812557871</v>
+      </c>
+      <c r="K86" t="s">
+        <v>110</v>
+      </c>
+      <c r="L86" s="3">
+        <v>-0.002106851851851852</v>
+      </c>
+      <c r="M86">
+        <v>-182.032</v>
+      </c>
+      <c r="N86" s="3">
+        <v>3.331458912037037</v>
+      </c>
+      <c r="O86">
+        <v>287838.05</v>
+      </c>
+      <c r="R86" t="s">
+        <v>115</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T86" s="3">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U86" t="b">
+        <v>0</v>
+      </c>
+      <c r="V86" t="s">
+        <v>121</v>
+      </c>
+      <c r="W86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23">
+      <c r="A87" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87" t="s">
+        <v>60</v>
+      </c>
+      <c r="C87" t="s">
+        <v>61</v>
+      </c>
+      <c r="D87" t="s">
+        <v>66</v>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H87" t="s">
+        <v>93</v>
+      </c>
+      <c r="I87" t="s">
+        <v>101</v>
+      </c>
+      <c r="J87" s="2">
+        <v>45916.95960697917</v>
+      </c>
+      <c r="K87" t="s">
+        <v>106</v>
+      </c>
+      <c r="L87" s="3">
+        <v>-0.03039960648148148</v>
+      </c>
+      <c r="M87">
+        <v>-2626.526</v>
+      </c>
+      <c r="N87" s="3">
+        <v>2.5429403125</v>
+      </c>
+      <c r="O87">
+        <v>219710.043</v>
+      </c>
+      <c r="R87" t="s">
+        <v>119</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="T87" s="3">
+        <v>3.395833333333333</v>
+      </c>
+      <c r="U87" t="b">
+        <v>0</v>
+      </c>
+      <c r="V87" t="s">
+        <v>121</v>
+      </c>
+      <c r="W87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23">
+      <c r="A88" t="s">
+        <v>44</v>
+      </c>
+      <c r="B88" t="s">
+        <v>60</v>
+      </c>
+      <c r="C88" t="s">
+        <v>61</v>
+      </c>
+      <c r="D88" t="s">
+        <v>67</v>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>83</v>
+      </c>
+      <c r="H88" t="s">
+        <v>93</v>
+      </c>
+      <c r="I88" t="s">
+        <v>99</v>
+      </c>
+      <c r="J88" s="2">
+        <v>45915.6401268287</v>
+      </c>
+      <c r="K88" t="s">
+        <v>106</v>
+      </c>
+      <c r="L88" s="3">
+        <v>-0.0001284259259259259</v>
+      </c>
+      <c r="M88">
+        <v>-11.096</v>
+      </c>
+      <c r="N88" s="3">
+        <v>1.223460162037037</v>
+      </c>
+      <c r="O88">
+        <v>105706.958</v>
+      </c>
+      <c r="R88" t="s">
+        <v>117</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T88" s="3">
         <v>1.833333333333333</v>
       </c>
-      <c r="U15" t="b">
-        <v>0</v>
-      </c>
-      <c r="V15" t="s">
-        <v>66</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="U88" t="b">
+        <v>0</v>
+      </c>
+      <c r="V88" t="s">
+        <v>121</v>
+      </c>
+      <c r="W88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23">
+      <c r="A89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89" t="s">
+        <v>60</v>
+      </c>
+      <c r="C89" t="s">
+        <v>61</v>
+      </c>
+      <c r="D89" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>83</v>
+      </c>
+      <c r="H89" t="s">
+        <v>93</v>
+      </c>
+      <c r="I89" t="s">
+        <v>100</v>
+      </c>
+      <c r="J89" s="2">
+        <v>45916.44111702546</v>
+      </c>
+      <c r="K89" t="s">
+        <v>103</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-0.0004208796296296296</v>
+      </c>
+      <c r="M89">
+        <v>-36.364</v>
+      </c>
+      <c r="N89" s="3">
+        <v>2.024450358796296</v>
+      </c>
+      <c r="O89">
+        <v>174912.511</v>
+      </c>
+      <c r="R89" t="s">
+        <v>118</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T89" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U89" t="b">
+        <v>0</v>
+      </c>
+      <c r="V89" t="s">
+        <v>121</v>
+      </c>
+      <c r="W89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23">
+      <c r="A90" t="s">
+        <v>46</v>
+      </c>
+      <c r="B90" t="s">
+        <v>60</v>
+      </c>
+      <c r="C90" t="s">
+        <v>61</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>83</v>
+      </c>
+      <c r="H90" t="s">
+        <v>93</v>
+      </c>
+      <c r="I90" t="s">
+        <v>100</v>
+      </c>
+      <c r="J90" s="2">
+        <v>45916.45647189815</v>
+      </c>
+      <c r="K90" t="s">
+        <v>107</v>
+      </c>
+      <c r="L90" s="3">
+        <v>-0.002893287037037037</v>
+      </c>
+      <c r="M90">
+        <v>-249.98</v>
+      </c>
+      <c r="N90" s="3">
+        <v>2.039805231481481</v>
+      </c>
+      <c r="O90">
+        <v>176239.172</v>
+      </c>
+      <c r="R90" t="s">
+        <v>118</v>
+      </c>
+      <c r="S90" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T90" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U90" t="b">
+        <v>0</v>
+      </c>
+      <c r="V90" t="s">
+        <v>121</v>
+      </c>
+      <c r="W90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23">
+      <c r="A91" t="s">
+        <v>47</v>
+      </c>
+      <c r="B91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C91" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" t="s">
+        <v>70</v>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>83</v>
+      </c>
+      <c r="H91" t="s">
+        <v>93</v>
+      </c>
+      <c r="I91" t="s">
+        <v>95</v>
+      </c>
+      <c r="J91" s="2">
+        <v>45918.5644958912</v>
+      </c>
+      <c r="K91" t="s">
+        <v>107</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-0.9004283333333334</v>
+      </c>
+      <c r="M91">
+        <v>-77797.008</v>
+      </c>
+      <c r="N91" s="3">
+        <v>4.147829224537037</v>
+      </c>
+      <c r="O91">
+        <v>358372.445</v>
+      </c>
+      <c r="R91" t="s">
+        <v>113</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T91" s="3">
+        <v>5.375</v>
+      </c>
+      <c r="U91" t="b">
+        <v>0</v>
+      </c>
+      <c r="V91" t="s">
+        <v>121</v>
+      </c>
+      <c r="W91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23">
+      <c r="A92" t="s">
+        <v>48</v>
+      </c>
+      <c r="B92" t="s">
+        <v>60</v>
+      </c>
+      <c r="C92" t="s">
+        <v>61</v>
+      </c>
+      <c r="D92" t="s">
+        <v>71</v>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>83</v>
+      </c>
+      <c r="H92" t="s">
+        <v>94</v>
+      </c>
+      <c r="I92" t="s">
+        <v>95</v>
+      </c>
+      <c r="J92" s="2">
+        <v>45919.6443719213</v>
+      </c>
+      <c r="K92" t="s">
+        <v>107</v>
+      </c>
+      <c r="L92" s="3">
+        <v>-0.03591431712962963</v>
+      </c>
+      <c r="M92">
+        <v>-3102.997</v>
+      </c>
+      <c r="N92" s="3">
+        <v>5.144371921296297</v>
+      </c>
+      <c r="O92">
+        <v>444473.734</v>
+      </c>
+      <c r="R92" t="s">
+        <v>113</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T92" s="3">
+        <v>5.375</v>
+      </c>
+      <c r="U92" t="b">
+        <v>0</v>
+      </c>
+      <c r="V92" t="s">
+        <v>121</v>
+      </c>
+      <c r="W92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23">
+      <c r="A93" t="s">
+        <v>49</v>
+      </c>
+      <c r="B93" t="s">
+        <v>60</v>
+      </c>
+      <c r="C93" t="s">
+        <v>61</v>
+      </c>
+      <c r="D93" t="s">
+        <v>72</v>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>83</v>
+      </c>
+      <c r="H93" t="s">
+        <v>94</v>
+      </c>
+      <c r="I93" t="s">
+        <v>97</v>
+      </c>
+      <c r="J93" s="2">
+        <v>45918.63040311343</v>
+      </c>
+      <c r="K93" t="s">
+        <v>107</v>
+      </c>
+      <c r="L93" s="3">
+        <v>-0.001639907407407407</v>
+      </c>
+      <c r="M93">
+        <v>-141.688</v>
+      </c>
+      <c r="N93" s="3">
+        <v>4.130403113425926</v>
+      </c>
+      <c r="O93">
+        <v>356866.829</v>
+      </c>
+      <c r="R93" t="s">
+        <v>115</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T93" s="3">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U93" t="b">
+        <v>0</v>
+      </c>
+      <c r="V93" t="s">
+        <v>121</v>
+      </c>
+      <c r="W93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23">
+      <c r="A94" t="s">
+        <v>50</v>
+      </c>
+      <c r="B94" t="s">
+        <v>60</v>
+      </c>
+      <c r="C94" t="s">
+        <v>61</v>
+      </c>
+      <c r="D94" t="s">
+        <v>73</v>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>83</v>
+      </c>
+      <c r="H94" t="s">
+        <v>93</v>
+      </c>
+      <c r="I94" t="s">
+        <v>97</v>
+      </c>
+      <c r="J94" s="2">
+        <v>45918.57802502315</v>
+      </c>
+      <c r="K94" t="s">
+        <v>107</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-0.0001042708333333333</v>
+      </c>
+      <c r="M94">
+        <v>-9.009</v>
+      </c>
+      <c r="N94" s="3">
+        <v>4.161358356481482</v>
+      </c>
+      <c r="O94">
+        <v>359541.362</v>
+      </c>
+      <c r="R94" t="s">
+        <v>115</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T94" s="3">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U94" t="b">
+        <v>0</v>
+      </c>
+      <c r="V94" t="s">
+        <v>121</v>
+      </c>
+      <c r="W94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23">
+      <c r="A95" t="s">
+        <v>51</v>
+      </c>
+      <c r="B95" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" t="s">
+        <v>61</v>
+      </c>
+      <c r="D95" t="s">
+        <v>74</v>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>83</v>
+      </c>
+      <c r="H95" t="s">
+        <v>94</v>
+      </c>
+      <c r="I95" t="s">
+        <v>97</v>
+      </c>
+      <c r="J95" s="2">
+        <v>45918.76002306713</v>
+      </c>
+      <c r="K95" t="s">
+        <v>111</v>
+      </c>
+      <c r="L95" s="3">
+        <v>-0.001359502314814815</v>
+      </c>
+      <c r="M95">
+        <v>-117.461</v>
+      </c>
+      <c r="N95" s="3">
+        <v>4.26002306712963</v>
+      </c>
+      <c r="O95">
+        <v>368065.993</v>
+      </c>
+      <c r="R95" t="s">
+        <v>115</v>
+      </c>
+      <c r="S95" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T95" s="3">
+        <v>4.458333333333333</v>
+      </c>
+      <c r="U95" t="b">
+        <v>0</v>
+      </c>
+      <c r="V95" t="s">
+        <v>121</v>
+      </c>
+      <c r="W95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23">
+      <c r="A96" t="s">
+        <v>52</v>
+      </c>
+      <c r="B96" t="s">
+        <v>60</v>
+      </c>
+      <c r="C96" t="s">
+        <v>61</v>
+      </c>
+      <c r="D96" t="s">
+        <v>75</v>
+      </c>
+      <c r="E96" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" t="s">
+        <v>86</v>
+      </c>
+      <c r="G96" t="s">
+        <v>88</v>
+      </c>
+      <c r="H96" t="s">
+        <v>93</v>
+      </c>
+      <c r="I96" t="s">
+        <v>99</v>
+      </c>
+      <c r="J96" s="2">
+        <v>45915.49003822917</v>
+      </c>
+      <c r="K96" t="s">
+        <v>86</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-0.1975464930555555</v>
+      </c>
+      <c r="M96">
+        <v>-17068.017</v>
+      </c>
+      <c r="N96" s="3">
+        <v>1.0733715625</v>
+      </c>
+      <c r="O96">
+        <v>92739.303</v>
+      </c>
+      <c r="P96" t="s">
+        <v>88</v>
+      </c>
+      <c r="R96" t="s">
+        <v>117</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T96" s="3">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U96" t="b">
+        <v>0</v>
+      </c>
+      <c r="V96" t="s">
+        <v>121</v>
+      </c>
+      <c r="W96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23">
+      <c r="A97" t="s">
+        <v>53</v>
+      </c>
+      <c r="B97" t="s">
+        <v>60</v>
+      </c>
+      <c r="C97" t="s">
+        <v>61</v>
+      </c>
+      <c r="D97" t="s">
+        <v>76</v>
+      </c>
+      <c r="E97" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>86</v>
+      </c>
+      <c r="G97" t="s">
+        <v>89</v>
+      </c>
+      <c r="H97" t="s">
+        <v>93</v>
+      </c>
+      <c r="I97" t="s">
+        <v>102</v>
+      </c>
+      <c r="J97" s="2">
+        <v>45914.98248302083</v>
+      </c>
+      <c r="K97" t="s">
+        <v>86</v>
+      </c>
+      <c r="L97" s="3">
+        <v>-0.0498675925925926</v>
+      </c>
+      <c r="M97">
+        <v>-4308.56</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0.5658163541666668</v>
+      </c>
+      <c r="O97">
+        <v>48886.533</v>
+      </c>
+      <c r="P97" t="s">
+        <v>102</v>
+      </c>
+      <c r="R97" t="s">
+        <v>120</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="U97" t="b">
+        <v>0</v>
+      </c>
+      <c r="V97" t="s">
+        <v>121</v>
+      </c>
+      <c r="W97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23">
+      <c r="A98" t="s">
+        <v>54</v>
+      </c>
+      <c r="B98" t="s">
+        <v>60</v>
+      </c>
+      <c r="C98" t="s">
+        <v>61</v>
+      </c>
+      <c r="D98" t="s">
+        <v>77</v>
+      </c>
+      <c r="E98" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>86</v>
+      </c>
+      <c r="G98" t="s">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s">
+        <v>93</v>
+      </c>
+      <c r="I98" t="s">
+        <v>100</v>
+      </c>
+      <c r="J98" s="2">
+        <v>45915.42726980324</v>
+      </c>
+      <c r="K98" t="s">
+        <v>86</v>
+      </c>
+      <c r="L98" s="3">
+        <v>-0.0001183796296296296</v>
+      </c>
+      <c r="M98">
+        <v>-10.228</v>
+      </c>
+      <c r="N98" s="3">
+        <v>1.010603136574074</v>
+      </c>
+      <c r="O98">
+        <v>87316.111</v>
+      </c>
+      <c r="P98" t="s">
+        <v>112</v>
+      </c>
+      <c r="R98" t="s">
+        <v>118</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T98" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U98" t="b">
+        <v>0</v>
+      </c>
+      <c r="V98" t="s">
+        <v>121</v>
+      </c>
+      <c r="W98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" t="s">
+        <v>61</v>
+      </c>
+      <c r="D99" t="s">
+        <v>78</v>
+      </c>
+      <c r="E99" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>86</v>
+      </c>
+      <c r="G99" t="s">
+        <v>89</v>
+      </c>
+      <c r="H99" t="s">
+        <v>93</v>
+      </c>
+      <c r="I99" t="s">
+        <v>102</v>
+      </c>
+      <c r="J99" s="2">
+        <v>45915.19124746528</v>
+      </c>
+      <c r="K99" t="s">
+        <v>86</v>
+      </c>
+      <c r="L99" s="3">
+        <v>-0.1664284259259259</v>
+      </c>
+      <c r="M99">
+        <v>-14379.416</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0.7745807986111112</v>
+      </c>
+      <c r="O99">
+        <v>66923.781</v>
+      </c>
+      <c r="P99" t="s">
+        <v>102</v>
+      </c>
+      <c r="R99" t="s">
+        <v>120</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="U99" t="b">
+        <v>0</v>
+      </c>
+      <c r="V99" t="s">
+        <v>121</v>
+      </c>
+      <c r="W99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23">
+      <c r="A100" t="s">
+        <v>56</v>
+      </c>
+      <c r="B100" t="s">
+        <v>60</v>
+      </c>
+      <c r="C100" t="s">
+        <v>61</v>
+      </c>
+      <c r="D100" t="s">
+        <v>79</v>
+      </c>
+      <c r="E100" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>86</v>
+      </c>
+      <c r="G100" t="s">
+        <v>89</v>
+      </c>
+      <c r="H100" t="s">
+        <v>94</v>
+      </c>
+      <c r="I100" t="s">
+        <v>102</v>
+      </c>
+      <c r="J100" s="2">
+        <v>45915.14697456019</v>
+      </c>
+      <c r="K100" t="s">
+        <v>86</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-0.04587693287037037</v>
+      </c>
+      <c r="M100">
+        <v>-3963.767</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0.6469745601851852</v>
+      </c>
+      <c r="O100">
+        <v>55898.602</v>
+      </c>
+      <c r="P100" t="s">
+        <v>102</v>
+      </c>
+      <c r="R100" t="s">
+        <v>120</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="U100" t="b">
+        <v>0</v>
+      </c>
+      <c r="V100" t="s">
+        <v>121</v>
+      </c>
+      <c r="W100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23">
+      <c r="A101" t="s">
+        <v>57</v>
+      </c>
+      <c r="B101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C101" t="s">
+        <v>61</v>
+      </c>
+      <c r="D101" t="s">
+        <v>80</v>
+      </c>
+      <c r="E101" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>86</v>
+      </c>
+      <c r="G101" t="s">
+        <v>89</v>
+      </c>
+      <c r="H101" t="s">
+        <v>94</v>
+      </c>
+      <c r="I101" t="s">
+        <v>102</v>
+      </c>
+      <c r="J101" s="2">
+        <v>45915.20803805556</v>
+      </c>
+      <c r="K101" t="s">
+        <v>86</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-0.0543519212962963</v>
+      </c>
+      <c r="M101">
+        <v>-4696.006</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0.7080380555555555</v>
+      </c>
+      <c r="O101">
+        <v>61174.488</v>
+      </c>
+      <c r="P101" t="s">
+        <v>102</v>
+      </c>
+      <c r="R101" t="s">
+        <v>120</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="U101" t="b">
+        <v>0</v>
+      </c>
+      <c r="V101" t="s">
+        <v>121</v>
+      </c>
+      <c r="W101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23">
+      <c r="A102" t="s">
+        <v>58</v>
+      </c>
+      <c r="B102" t="s">
+        <v>60</v>
+      </c>
+      <c r="C102" t="s">
+        <v>61</v>
+      </c>
+      <c r="D102" t="s">
+        <v>81</v>
+      </c>
+      <c r="E102" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" t="s">
+        <v>86</v>
+      </c>
+      <c r="G102" t="s">
+        <v>91</v>
+      </c>
+      <c r="H102" t="s">
+        <v>94</v>
+      </c>
+      <c r="I102" t="s">
+        <v>96</v>
+      </c>
+      <c r="J102" s="2">
+        <v>45917.80574773148</v>
+      </c>
+      <c r="K102" t="s">
+        <v>86</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-0.02553084490740741</v>
+      </c>
+      <c r="M102">
+        <v>-2205.865</v>
+      </c>
+      <c r="N102" s="3">
+        <v>3.305747731481481</v>
+      </c>
+      <c r="O102">
+        <v>285616.604</v>
+      </c>
+      <c r="P102" t="s">
+        <v>91</v>
+      </c>
+      <c r="R102" t="s">
+        <v>114</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T102" s="3">
+        <v>3.625</v>
+      </c>
+      <c r="U102" t="b">
+        <v>0</v>
+      </c>
+      <c r="V102" t="s">
+        <v>121</v>
+      </c>
+      <c r="W102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23">
+      <c r="A103" t="s">
+        <v>59</v>
+      </c>
+      <c r="B103" t="s">
+        <v>60</v>
+      </c>
+      <c r="C103" t="s">
+        <v>61</v>
+      </c>
+      <c r="D103" t="s">
+        <v>82</v>
+      </c>
+      <c r="E103" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s">
+        <v>86</v>
+      </c>
+      <c r="G103" t="s">
+        <v>89</v>
+      </c>
+      <c r="H103" t="s">
+        <v>94</v>
+      </c>
+      <c r="I103" t="s">
+        <v>102</v>
+      </c>
+      <c r="J103" s="2">
+        <v>45915.15566939815</v>
+      </c>
+      <c r="K103" t="s">
+        <v>86</v>
+      </c>
+      <c r="L103" s="3">
+        <v>-0.1091181712962963</v>
+      </c>
+      <c r="M103">
+        <v>-9427.809999999999</v>
+      </c>
+      <c r="N103" s="3">
+        <v>0.6556693981481482</v>
+      </c>
+      <c r="O103">
+        <v>56649.836</v>
+      </c>
+      <c r="P103" t="s">
+        <v>102</v>
+      </c>
+      <c r="R103" t="s">
+        <v>120</v>
+      </c>
+      <c r="S103" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T103" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="U103" t="b">
+        <v>0</v>
+      </c>
+      <c r="V103" t="s">
+        <v>121</v>
+      </c>
+      <c r="W103" t="b">
         <v>0</v>
       </c>
     </row>
